--- a/DPOPz DATABASE.xlsx
+++ b/DPOPz DATABASE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/home/Coding Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NY-NT-215\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1DA2BC-6965-3345-BD28-53BD4AA793B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA42BA0-C611-4874-9D57-7C5EAB172BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="600" windowWidth="31620" windowHeight="19880" xr2:uid="{E04FA07E-3229-C048-A4EF-F04BD1865DFB}"/>
+    <workbookView xWindow="30540" yWindow="16200" windowWidth="14610" windowHeight="15585" xr2:uid="{E04FA07E-3229-C048-A4EF-F04BD1865DFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15388" uniqueCount="1043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17062" uniqueCount="1048">
   <si>
     <t>Timestamp</t>
   </si>
@@ -3173,6 +3173,25 @@
   </si>
   <si>
     <t>ON</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>海神</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>1116</t>
+  </si>
+  <si>
+    <t>1899_RAW</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -3180,7 +3199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3294,7 +3313,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Hiragino Sans"/>
-      <charset val="128"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3319,7 +3345,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3371,6 +3397,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3389,9 +3418,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3429,7 +3458,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3535,7 +3564,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3677,7 +3706,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3685,14 +3714,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A56080C3-134C-2143-A287-57FAE1DA4112}">
-  <dimension ref="A1:F2078"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <dimension ref="A1:F2357"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -27815,7 +27844,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1207" spans="1:6" ht="30">
+    <row r="1207" spans="1:6" ht="24">
       <c r="A1207" s="2" t="s">
         <v>691</v>
       </c>
@@ -45253,6 +45282,5586 @@
       </c>
       <c r="F2078" s="2" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:6">
+      <c r="A2079" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>692</v>
+      </c>
+      <c r="C2079" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2079" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2079" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2079" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:6">
+      <c r="A2080" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2080" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2080" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2080" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:6">
+      <c r="A2081" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2081" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2081" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2081" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2081" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:6">
+      <c r="A2082" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2082" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2082" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2082" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2082" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:6">
+      <c r="A2083" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2083" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2083" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2083" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2083" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:6">
+      <c r="A2084" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2084" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2084" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2084" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2084" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:6">
+      <c r="A2085" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2085" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2085" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2085" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2085" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:6">
+      <c r="A2086" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2086" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2086" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2086" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2086" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:6">
+      <c r="A2087" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2087" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2087" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2087" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2087" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:6">
+      <c r="A2088" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2088" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2088" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2088" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:6">
+      <c r="A2089" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2089" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2089" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2089" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2089" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:6">
+      <c r="A2090" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2090" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2090" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2090" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:6">
+      <c r="A2091" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2091" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2091" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2091" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2091" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:6">
+      <c r="A2092" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2092" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2092" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2092" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2092" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:6">
+      <c r="A2093" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2093" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2093" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2093" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2093" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:6">
+      <c r="A2094" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2094" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2094" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2094" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2094" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:6">
+      <c r="A2095" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2095" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2095" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2095" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2095" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:6">
+      <c r="A2096" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2096" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2096" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2096" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2096" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:6">
+      <c r="A2097" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2097" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2097" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2097" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2097" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:6">
+      <c r="A2098" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2098" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2098" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2098" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2098" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:6">
+      <c r="A2099" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2099" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2099" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2099" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2099" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:6">
+      <c r="A2100" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2100" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2100" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2100" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2100" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:6">
+      <c r="A2101" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2101" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2101" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2101" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:6">
+      <c r="A2102" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2102" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2102" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2102" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:6">
+      <c r="A2103" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2103" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2103" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2103" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:6">
+      <c r="A2104" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2104" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2104" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2104" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2104" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:6">
+      <c r="A2105" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2105" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2105" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2105" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2105" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:6">
+      <c r="A2106" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2106" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2106" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2106" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2106" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:6">
+      <c r="A2107" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2107" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2107" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2107" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:6">
+      <c r="A2108" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2108" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2108" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2108" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:6">
+      <c r="A2109" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2109" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2109" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2109" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:6">
+      <c r="A2110" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2110" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2110" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2110" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:6">
+      <c r="A2111" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2111" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2111" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2111" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2111" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:6">
+      <c r="A2112" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2112" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:6">
+      <c r="A2113" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2113" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:6">
+      <c r="A2114" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:6">
+      <c r="A2115" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2115" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:6">
+      <c r="A2116" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2116" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:6">
+      <c r="A2117" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2117" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:6">
+      <c r="A2118" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2118" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:6">
+      <c r="A2119" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2119" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:6">
+      <c r="A2120" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2120" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:6">
+      <c r="A2121" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2121" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:6">
+      <c r="A2122" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2122" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:6">
+      <c r="A2123" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2123" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:6">
+      <c r="A2124" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2124" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2124" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:6">
+      <c r="A2125" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2125" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2125" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:6">
+      <c r="A2126" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2126" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2126" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2126" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:6">
+      <c r="A2127" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2127" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2127" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2127" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:6">
+      <c r="A2128" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2128" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2128" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2128" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2128" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:6">
+      <c r="A2129" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2129" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2129" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2129" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:6">
+      <c r="A2130" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2130" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2130" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2130" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:6">
+      <c r="A2131" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2131" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2131" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:6">
+      <c r="A2132" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2132" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2132" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:6">
+      <c r="A2133" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2133" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2133" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2133" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:6">
+      <c r="A2134" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2134" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2134" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:6">
+      <c r="A2135" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2135" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2135" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2135" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:6">
+      <c r="A2136" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2136" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2136" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2136" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2136" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:6">
+      <c r="A2137" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2137" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2137" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2137" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:6">
+      <c r="A2138" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2138" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2138" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2138" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2138" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:6">
+      <c r="A2139" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2139" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2139" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2139" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2139" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:6">
+      <c r="A2140" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2140" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2140" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2140" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2140" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2140" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:6">
+      <c r="A2141" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2141" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2141" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2141" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2141" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:6">
+      <c r="A2142" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2142" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2142" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2142" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2142" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2142" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:6">
+      <c r="A2143" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2143" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2143" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2143" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2143" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2143" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:6">
+      <c r="A2144" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2144" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2144" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2144" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2144" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:6">
+      <c r="A2145" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2145" t="s">
+        <v>173</v>
+      </c>
+      <c r="C2145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2145" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2145" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2145" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:6">
+      <c r="A2146" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2146" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2146" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2146" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2146" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2146" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:6">
+      <c r="A2147" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2147" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2147" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2147" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2147" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2147" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:6">
+      <c r="A2148" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2148" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2148" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2148" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2148" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:6">
+      <c r="A2149" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2149" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2149" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2149" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2149" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:6">
+      <c r="A2150" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2150" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2150" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2150" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:6">
+      <c r="A2151" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2151" t="s">
+        <v>181</v>
+      </c>
+      <c r="C2151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2151" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2151" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2151" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:6">
+      <c r="A2152" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2152" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2152" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2152" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2152" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2152" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:6">
+      <c r="A2153" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2153" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2153" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2153" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2153" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:6">
+      <c r="A2154" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2154" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2154" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2154" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2154" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:6">
+      <c r="A2155" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2155" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2155" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2155" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2155" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2155" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:6">
+      <c r="A2156" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2156" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2156" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2156" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2156" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2156" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:6">
+      <c r="A2157" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2157" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2157" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2157" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2157" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2157" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:6">
+      <c r="A2158" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2158" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2158" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2158" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2158" t="s">
+        <v>693</v>
+      </c>
+      <c r="F2158" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:6">
+      <c r="A2159" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2159" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2159" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2159" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2159" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2159" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:6">
+      <c r="A2160" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2160" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2160" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2160" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2160" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2160" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:6">
+      <c r="A2161" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2161" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2161" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2161" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2161" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2161" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:6">
+      <c r="A2162" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2162" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2162" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2162" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2162" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2162" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:6">
+      <c r="A2163" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2163" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2163" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2163" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2163" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:6">
+      <c r="A2164" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2164" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2164" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2164" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2164" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2164" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:6">
+      <c r="A2165" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2165" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2165" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2165" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2165" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:6">
+      <c r="A2166" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2166" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2166" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2166" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2166" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:6">
+      <c r="A2167" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2167" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2167" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2167" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2167" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2167" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:6">
+      <c r="A2168" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2168" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2168" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2168" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2168" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2168" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:6">
+      <c r="A2169" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2169" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2169" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2169" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2169" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:6">
+      <c r="A2170" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2170" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2170" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2170" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2170" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2170" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:6">
+      <c r="A2171" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2171" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2171" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2171" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2171" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2171" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:6">
+      <c r="A2172" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2172" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2172" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2172" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2172" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:6">
+      <c r="A2173" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2173" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2173" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2173" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2173" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:6">
+      <c r="A2174" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2174" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2174" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2174" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2174" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:6">
+      <c r="A2175" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2175" t="s">
+        <v>237</v>
+      </c>
+      <c r="C2175" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2175" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2175" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2175" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:6">
+      <c r="A2176" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2176" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2176" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2176" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2176" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2176" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:6">
+      <c r="A2177" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2177" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2177" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2177" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2177" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2177" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:6">
+      <c r="A2178" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2178" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2178" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2178" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2178" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2178" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:6">
+      <c r="A2179" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2179" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2179" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2179" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2179" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:6">
+      <c r="A2180" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2180" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2180" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2180" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2180" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2180" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:6">
+      <c r="A2181" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2181" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2181" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2181" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2181" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2181" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:6">
+      <c r="A2182" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2182" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2182" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2182" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2182" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2182" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:6">
+      <c r="A2183" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2183" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2183" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2183" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2183" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2183" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:6">
+      <c r="A2184" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2184" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2184" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2184" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2184" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:6">
+      <c r="A2185" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2185" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2185" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2185" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2185" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2185" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:6">
+      <c r="A2186" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2186" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2186" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2186" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2186" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2186" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:6">
+      <c r="A2187" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2187" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2187" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2187" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2187" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:6">
+      <c r="A2188" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2188" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2188" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2188" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2188" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2188" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:6">
+      <c r="A2189" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2189" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2189" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2189" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2189" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:6">
+      <c r="A2190" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2190" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2190" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2190" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2190" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2190" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:6">
+      <c r="A2191" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2191" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2191" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2191" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2191" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2191" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:6">
+      <c r="A2192" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2192" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2192" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2192" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2192" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2192" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:6">
+      <c r="A2193" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2193" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2193" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2193" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2193" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:6">
+      <c r="A2194" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2194" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2194" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2194" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2194" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:6">
+      <c r="A2195" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2195" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2195" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2195" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2195" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:6">
+      <c r="A2196" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2196" t="s">
+        <v>295</v>
+      </c>
+      <c r="C2196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2196" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2196" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2196" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:6">
+      <c r="A2197" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2197" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2197" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2197" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2197" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2197" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:6">
+      <c r="A2198" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2198" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2198" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2198" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2198" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2198" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:6">
+      <c r="A2199" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2199" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2199" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2199" t="s">
+        <v>697</v>
+      </c>
+      <c r="F2199" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:6">
+      <c r="A2200" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2200" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2200" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2200" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2200" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:6">
+      <c r="A2201" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2201" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2201" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2201" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2201" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2201" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:6">
+      <c r="A2202" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2202" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2202" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2202" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2202" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:6">
+      <c r="A2203" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2203" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2203" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2203" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2203" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:6">
+      <c r="A2204" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2204" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2204" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2204" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2204" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:6">
+      <c r="A2205" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2205" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2205" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2205" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2205" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:6">
+      <c r="A2206" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2206" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2206" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2206" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2206" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:6">
+      <c r="A2207" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2207" t="s">
+        <v>313</v>
+      </c>
+      <c r="C2207" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2207" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2207" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2207" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:6">
+      <c r="A2208" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2208" t="s">
+        <v>315</v>
+      </c>
+      <c r="C2208" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2208" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2208" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2208" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:6">
+      <c r="A2209" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2209" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2209" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2209" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2209" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:6">
+      <c r="A2210" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2210" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2210" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2210" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2210" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:6">
+      <c r="A2211" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2211" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2211" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2211" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2211" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2211" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:6">
+      <c r="A2212" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2212" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2212" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2212" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2212" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:6">
+      <c r="A2213" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2213" t="s">
+        <v>328</v>
+      </c>
+      <c r="C2213" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2213" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2213" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2213" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:6">
+      <c r="A2214" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2214" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2214" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2214" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2214" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:6">
+      <c r="A2215" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2215" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2215" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2215" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2215" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2215" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:6">
+      <c r="A2216" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2216" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2216" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2216" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2216" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:6">
+      <c r="A2217" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2217" t="s">
+        <v>338</v>
+      </c>
+      <c r="C2217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2217" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2217" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2217" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:6">
+      <c r="A2218" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2218" t="s">
+        <v>341</v>
+      </c>
+      <c r="C2218" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2218" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2218" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2218" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:6">
+      <c r="A2219" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2219" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2219" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2219" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2219" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:6">
+      <c r="A2220" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2220" t="s">
+        <v>351</v>
+      </c>
+      <c r="C2220" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2220" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2220" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2220" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:6">
+      <c r="A2221" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2221" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2221" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2221" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2221" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:6">
+      <c r="A2222" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2222" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2222" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2222" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2222" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2222" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:6">
+      <c r="A2223" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2223" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2223" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2223" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2223" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:6">
+      <c r="A2224" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2224" t="s">
+        <v>359</v>
+      </c>
+      <c r="C2224" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2224" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2224" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2224" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:6">
+      <c r="A2225" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2225" t="s">
+        <v>360</v>
+      </c>
+      <c r="C2225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2225" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2225" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2225" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:6">
+      <c r="A2226" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2226" t="s">
+        <v>361</v>
+      </c>
+      <c r="C2226" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2226" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2226" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2226" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:6">
+      <c r="A2227" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2227" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2227" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2227" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2227" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2227" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:6">
+      <c r="A2228" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2228" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2228" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2228" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2228" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2228" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:6">
+      <c r="A2229" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2229" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2229" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2229" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2229" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:6">
+      <c r="A2230" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2230" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2230" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2230" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2230" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2230" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:6">
+      <c r="A2231" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>374</v>
+      </c>
+      <c r="C2231" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2231" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2231" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2231" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:6">
+      <c r="A2232" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2232" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2232" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2232" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2232" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:6">
+      <c r="A2233" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2233" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2233" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2233" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2233" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:6">
+      <c r="A2234" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2234" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2234" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2234" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:6">
+      <c r="A2235" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2235" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2235" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2235" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2235" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:6">
+      <c r="A2236" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2236" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2236" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2236" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2236" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:6">
+      <c r="A2237" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>395</v>
+      </c>
+      <c r="C2237" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2237" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2237" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2237" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:6">
+      <c r="A2238" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2238" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2238" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2238" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2238" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:6">
+      <c r="A2239" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2239" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2239" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2239" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2239" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:6">
+      <c r="A2240" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>400</v>
+      </c>
+      <c r="C2240" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2240" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2240" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2240" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:6">
+      <c r="A2241" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>403</v>
+      </c>
+      <c r="C2241" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2241" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2241" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2241" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:6">
+      <c r="A2242" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2242" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2242" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2242" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2242" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:6">
+      <c r="A2243" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2243" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2243" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2243" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2243" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:6">
+      <c r="A2244" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>406</v>
+      </c>
+      <c r="C2244" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2244" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2244" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:6">
+      <c r="A2245" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>407</v>
+      </c>
+      <c r="C2245" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2245" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2245" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2245" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:6">
+      <c r="A2246" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2246" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2246" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2246" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2246" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:6">
+      <c r="A2247" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2247" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2247" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2247" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2247" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:6">
+      <c r="A2248" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>415</v>
+      </c>
+      <c r="C2248" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2248" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2248" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2248" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:6">
+      <c r="A2249" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2249" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2249" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2249" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2249" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:6">
+      <c r="A2250" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>421</v>
+      </c>
+      <c r="C2250" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2250" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2250" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2250" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:6">
+      <c r="A2251" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>423</v>
+      </c>
+      <c r="C2251" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2251" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2251" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2251" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:6">
+      <c r="A2252" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2252" t="s">
+        <v>429</v>
+      </c>
+      <c r="C2252" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2252" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2252" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2252" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:6">
+      <c r="A2253" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2253" t="s">
+        <v>430</v>
+      </c>
+      <c r="C2253" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2253" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2253" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2253" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:6">
+      <c r="A2254" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2254" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2254" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2254" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2254" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:6">
+      <c r="A2255" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>434</v>
+      </c>
+      <c r="C2255" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2255" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2255" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2255" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:6">
+      <c r="A2256" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2256" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2256" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2256" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2256" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2256" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:6">
+      <c r="A2257" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2257" t="s">
+        <v>440</v>
+      </c>
+      <c r="C2257" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2257" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2257" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2257" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:6">
+      <c r="A2258" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2258" t="s">
+        <v>442</v>
+      </c>
+      <c r="C2258" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2258" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2258" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2258" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:6">
+      <c r="A2259" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2259" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2259" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2259" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2259" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2259" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:6">
+      <c r="A2260" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2260" t="s">
+        <v>454</v>
+      </c>
+      <c r="C2260" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2260" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2260" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2260" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:6">
+      <c r="A2261" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>460</v>
+      </c>
+      <c r="C2261" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2261" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2261" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2261" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:6">
+      <c r="A2262" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>461</v>
+      </c>
+      <c r="C2262" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2262" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2262" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2262" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:6">
+      <c r="A2263" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2263" t="s">
+        <v>462</v>
+      </c>
+      <c r="C2263" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2263" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2263" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2263" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:6">
+      <c r="A2264" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2264" t="s">
+        <v>466</v>
+      </c>
+      <c r="C2264" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2264" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2264" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:6">
+      <c r="A2265" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2265" t="s">
+        <v>468</v>
+      </c>
+      <c r="C2265" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2265" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2265" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2265" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:6">
+      <c r="A2266" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2266" t="s">
+        <v>474</v>
+      </c>
+      <c r="C2266" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2266" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2266" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:6">
+      <c r="A2267" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2267" t="s">
+        <v>475</v>
+      </c>
+      <c r="C2267" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2267" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2267" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2267" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:6">
+      <c r="A2268" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2268" t="s">
+        <v>476</v>
+      </c>
+      <c r="C2268" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2268" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2268" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:6">
+      <c r="A2269" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2269" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2269" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2269" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2269" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:6">
+      <c r="A2270" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2270" t="s">
+        <v>480</v>
+      </c>
+      <c r="C2270" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2270" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2270" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:6">
+      <c r="A2271" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2271" t="s">
+        <v>482</v>
+      </c>
+      <c r="C2271" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2271" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2271" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2271" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:6">
+      <c r="A2272" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>483</v>
+      </c>
+      <c r="C2272" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2272" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2272" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:6">
+      <c r="A2273" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2273" t="s">
+        <v>485</v>
+      </c>
+      <c r="C2273" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2273" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2273" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2273" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:6">
+      <c r="A2274" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2274" t="s">
+        <v>488</v>
+      </c>
+      <c r="C2274" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2274" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2274" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:6">
+      <c r="A2275" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2275" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2275" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2275" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2275" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2275" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:6">
+      <c r="A2276" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2276" t="s">
+        <v>489</v>
+      </c>
+      <c r="C2276" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2276" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2276" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:6">
+      <c r="A2277" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2277" t="s">
+        <v>491</v>
+      </c>
+      <c r="C2277" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2277" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2277" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2277" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:6">
+      <c r="A2278" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2278" t="s">
+        <v>493</v>
+      </c>
+      <c r="C2278" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2278" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2278" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:6">
+      <c r="A2279" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2279" t="s">
+        <v>495</v>
+      </c>
+      <c r="C2279" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2279" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2279" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2279" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:6">
+      <c r="A2280" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2280" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2280" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2280" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2280" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:6">
+      <c r="A2281" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2281" t="s">
+        <v>504</v>
+      </c>
+      <c r="C2281" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2281" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2281" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2281" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:6">
+      <c r="A2282" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2282" t="s">
+        <v>507</v>
+      </c>
+      <c r="C2282" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2282" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2282" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:6">
+      <c r="A2283" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2283" t="s">
+        <v>508</v>
+      </c>
+      <c r="C2283" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2283" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2283" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2283" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:6">
+      <c r="A2284" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2284" t="s">
+        <v>508</v>
+      </c>
+      <c r="C2284" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2284" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2284" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:6">
+      <c r="A2285" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2285" t="s">
+        <v>518</v>
+      </c>
+      <c r="C2285" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2285" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2285" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2285" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:6">
+      <c r="A2286" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2286" t="s">
+        <v>519</v>
+      </c>
+      <c r="C2286" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2286" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2286" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:6">
+      <c r="A2287" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2287" t="s">
+        <v>520</v>
+      </c>
+      <c r="C2287" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2287" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2287" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:6">
+      <c r="A2288" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2288" t="s">
+        <v>527</v>
+      </c>
+      <c r="C2288" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2288" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2288" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:6">
+      <c r="A2289" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2289" t="s">
+        <v>535</v>
+      </c>
+      <c r="C2289" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2289" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2289" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2289" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:6">
+      <c r="A2290" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2290" t="s">
+        <v>540</v>
+      </c>
+      <c r="C2290" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2290" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2290" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:6">
+      <c r="A2291" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2291" t="s">
+        <v>541</v>
+      </c>
+      <c r="C2291" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2291" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2291" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:6">
+      <c r="A2292" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2292" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C2292" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2292" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2292" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:6">
+      <c r="A2293" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2293" t="s">
+        <v>543</v>
+      </c>
+      <c r="C2293" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2293" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2293" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:6">
+      <c r="A2294" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2294" t="s">
+        <v>549</v>
+      </c>
+      <c r="C2294" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2294" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2294" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:6">
+      <c r="A2295" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2295" t="s">
+        <v>549</v>
+      </c>
+      <c r="C2295" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2295" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2295" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2295" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:6">
+      <c r="A2296" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2296" t="s">
+        <v>556</v>
+      </c>
+      <c r="C2296" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2296" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2296" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2296" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:6">
+      <c r="A2297" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2297" t="s">
+        <v>557</v>
+      </c>
+      <c r="C2297" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2297" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2297" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2297" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:6">
+      <c r="A2298" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2298" t="s">
+        <v>559</v>
+      </c>
+      <c r="C2298" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2298" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2298" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2298" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:6">
+      <c r="A2299" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2299" t="s">
+        <v>560</v>
+      </c>
+      <c r="C2299" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2299" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2299" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2299" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:6">
+      <c r="A2300" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2300" t="s">
+        <v>560</v>
+      </c>
+      <c r="C2300" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2300" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2300" t="s">
+        <v>693</v>
+      </c>
+      <c r="F2300" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:6">
+      <c r="A2301" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2301" t="s">
+        <v>561</v>
+      </c>
+      <c r="C2301" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2301" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2301" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2301" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:6">
+      <c r="A2302" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2302" t="s">
+        <v>563</v>
+      </c>
+      <c r="C2302" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2302" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2302" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2302" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:6">
+      <c r="A2303" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2303" t="s">
+        <v>569</v>
+      </c>
+      <c r="C2303" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2303" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2303" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2303" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:6">
+      <c r="A2304" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2304" t="s">
+        <v>569</v>
+      </c>
+      <c r="C2304" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2304" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2304" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2304" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:6">
+      <c r="A2305" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2305" t="s">
+        <v>570</v>
+      </c>
+      <c r="C2305" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2305" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2305" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2305" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:6">
+      <c r="A2306" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2306" t="s">
+        <v>571</v>
+      </c>
+      <c r="C2306" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2306" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2306" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2306" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:6">
+      <c r="A2307" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2307" t="s">
+        <v>579</v>
+      </c>
+      <c r="C2307" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2307" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2307" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:6">
+      <c r="A2308" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2308" t="s">
+        <v>580</v>
+      </c>
+      <c r="C2308" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2308" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2308" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2308" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:6">
+      <c r="A2309" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2309" t="s">
+        <v>582</v>
+      </c>
+      <c r="C2309" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2309" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2309" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:6">
+      <c r="A2310" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2310" t="s">
+        <v>585</v>
+      </c>
+      <c r="C2310" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2310" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2310" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2310" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:6">
+      <c r="A2311" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2311" t="s">
+        <v>593</v>
+      </c>
+      <c r="C2311" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2311" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2311" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:6">
+      <c r="A2312" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2312" t="s">
+        <v>594</v>
+      </c>
+      <c r="C2312" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2312" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2312" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2312" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:6">
+      <c r="A2313" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2313" t="s">
+        <v>595</v>
+      </c>
+      <c r="C2313" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2313" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2313" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:6">
+      <c r="A2314" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2314" t="s">
+        <v>598</v>
+      </c>
+      <c r="C2314" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2314" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2314" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:6">
+      <c r="A2315" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2315" t="s">
+        <v>598</v>
+      </c>
+      <c r="C2315" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2315" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2315" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:6">
+      <c r="A2316" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2316" t="s">
+        <v>600</v>
+      </c>
+      <c r="C2316" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2316" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2316" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2316" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:6">
+      <c r="A2317" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2317" t="s">
+        <v>601</v>
+      </c>
+      <c r="C2317" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2317" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2317" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:6">
+      <c r="A2318" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2318" t="s">
+        <v>606</v>
+      </c>
+      <c r="C2318" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2318" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2318" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2318" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:6">
+      <c r="A2319" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2319" t="s">
+        <v>620</v>
+      </c>
+      <c r="C2319" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2319" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2319" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:6">
+      <c r="A2320" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2320" t="s">
+        <v>621</v>
+      </c>
+      <c r="C2320" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2320" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2320" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2320" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:6">
+      <c r="A2321" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2321" t="s">
+        <v>622</v>
+      </c>
+      <c r="C2321" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2321" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2321" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:6">
+      <c r="A2322" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2322" t="s">
+        <v>624</v>
+      </c>
+      <c r="C2322" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2322" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2322" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:6">
+      <c r="A2323" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2323" t="s">
+        <v>625</v>
+      </c>
+      <c r="C2323" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2323" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2323" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:6">
+      <c r="A2324" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2324" t="s">
+        <v>629</v>
+      </c>
+      <c r="C2324" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2324" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2324" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:6">
+      <c r="A2325" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2325" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2325" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2325" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2325" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2325" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:6">
+      <c r="A2326" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2326" t="s">
+        <v>633</v>
+      </c>
+      <c r="C2326" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2326" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2326" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:6">
+      <c r="A2327" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2327" t="s">
+        <v>635</v>
+      </c>
+      <c r="C2327" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2327" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2327" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2327" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:6">
+      <c r="A2328" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2328" t="s">
+        <v>637</v>
+      </c>
+      <c r="C2328" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2328" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2328" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:6">
+      <c r="A2329" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2329" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2329" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2329" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2329" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2329" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:6">
+      <c r="A2330" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2330" t="s">
+        <v>641</v>
+      </c>
+      <c r="C2330" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2330" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2330" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:6">
+      <c r="A2331" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2331" t="s">
+        <v>642</v>
+      </c>
+      <c r="C2331" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2331" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2331" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:6">
+      <c r="A2332" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2332" t="s">
+        <v>643</v>
+      </c>
+      <c r="C2332" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2332" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2332" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:6">
+      <c r="A2333" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2333" t="s">
+        <v>644</v>
+      </c>
+      <c r="C2333" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2333" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2333" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:6">
+      <c r="A2334" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2334" t="s">
+        <v>645</v>
+      </c>
+      <c r="C2334" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2334" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2334" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:6">
+      <c r="A2335" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2335" t="s">
+        <v>646</v>
+      </c>
+      <c r="C2335" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2335" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2335" t="s">
+        <v>697</v>
+      </c>
+      <c r="F2335" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:6">
+      <c r="A2336" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2336" t="s">
+        <v>647</v>
+      </c>
+      <c r="C2336" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2336" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2336" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:6">
+      <c r="A2337" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2337" t="s">
+        <v>652</v>
+      </c>
+      <c r="C2337" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2337" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2337" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:6">
+      <c r="A2338" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2338" t="s">
+        <v>656</v>
+      </c>
+      <c r="C2338" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2338" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2338" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:6">
+      <c r="A2339" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2339" t="s">
+        <v>657</v>
+      </c>
+      <c r="C2339" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2339" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2339" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:6">
+      <c r="A2340" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2340" t="s">
+        <v>659</v>
+      </c>
+      <c r="C2340" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2340" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2340" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2340" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:6">
+      <c r="A2341" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2341" t="s">
+        <v>660</v>
+      </c>
+      <c r="C2341" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2341" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2341" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:6">
+      <c r="A2342" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2342" t="s">
+        <v>662</v>
+      </c>
+      <c r="C2342" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2342" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2342" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2342" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:6">
+      <c r="A2343" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2343" t="s">
+        <v>663</v>
+      </c>
+      <c r="C2343" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2343" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2343" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2343" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:6">
+      <c r="A2344" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2344" t="s">
+        <v>663</v>
+      </c>
+      <c r="C2344" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2344" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2344" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2344" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:6">
+      <c r="A2345" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2345" t="s">
+        <v>666</v>
+      </c>
+      <c r="C2345" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2345" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2345" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2345" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:6">
+      <c r="A2346" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2346" t="s">
+        <v>668</v>
+      </c>
+      <c r="C2346" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2346" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2346" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2346" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:6">
+      <c r="A2347" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2347" t="s">
+        <v>670</v>
+      </c>
+      <c r="C2347" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2347" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2347" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2347" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:6">
+      <c r="A2348" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2348" t="s">
+        <v>673</v>
+      </c>
+      <c r="C2348" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2348" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2348" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2348" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:6">
+      <c r="A2349" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2349" t="s">
+        <v>675</v>
+      </c>
+      <c r="C2349" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2349" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2349" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2349" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:6">
+      <c r="A2350" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2350" t="s">
+        <v>677</v>
+      </c>
+      <c r="C2350" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2350" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2350" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2350" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:6">
+      <c r="A2351" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2351" t="s">
+        <v>679</v>
+      </c>
+      <c r="C2351" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2351" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2351" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2351" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:6">
+      <c r="A2352" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2352" t="s">
+        <v>680</v>
+      </c>
+      <c r="C2352" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2352" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2352" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2352" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:6">
+      <c r="A2353" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2353" t="s">
+        <v>682</v>
+      </c>
+      <c r="C2353" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2353" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2353" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2353" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:6">
+      <c r="A2354" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2354" t="s">
+        <v>687</v>
+      </c>
+      <c r="C2354" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2354" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2354" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2354" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:6">
+      <c r="A2355" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2355" t="s">
+        <v>688</v>
+      </c>
+      <c r="C2355" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2355" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2355" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2355" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:6">
+      <c r="A2356" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2356" t="s">
+        <v>689</v>
+      </c>
+      <c r="C2356" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2356" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2356" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2356" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:6">
+      <c r="A2357" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2357" t="s">
+        <v>690</v>
+      </c>
+      <c r="C2357" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2357" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2357" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2357" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -45265,12 +50874,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F2257CA-8CC2-EA47-AF30-163EC9F9B364}">
   <dimension ref="A1:W730"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25"/>
   <cols>
-    <col min="2" max="2" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -50895,7 +56505,7 @@
         <v>221</v>
       </c>
       <c r="D234" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E234" s="13">
         <v>12</v>
@@ -51039,7 +56649,7 @@
         <v>226</v>
       </c>
       <c r="D240" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E240" s="13">
         <v>12</v>
@@ -51111,7 +56721,7 @@
         <v>229</v>
       </c>
       <c r="D243" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E243" s="13">
         <v>12</v>
@@ -51159,7 +56769,7 @@
         <v>231</v>
       </c>
       <c r="D245" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E245" s="13">
         <v>12</v>
@@ -51207,7 +56817,7 @@
         <v>232</v>
       </c>
       <c r="D247" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E247" s="13">
         <v>12</v>
@@ -51279,7 +56889,7 @@
         <v>235</v>
       </c>
       <c r="D250" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E250" s="13">
         <v>12</v>
@@ -51471,7 +57081,7 @@
         <v>242</v>
       </c>
       <c r="D258" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E258" s="13">
         <v>12</v>
@@ -51567,7 +57177,7 @@
         <v>246</v>
       </c>
       <c r="D262" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E262" s="13">
         <v>12</v>
@@ -51615,7 +57225,7 @@
         <v>247</v>
       </c>
       <c r="D264" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E264" s="13">
         <v>12</v>
@@ -51687,7 +57297,7 @@
         <v>250</v>
       </c>
       <c r="D267" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E267" s="13">
         <v>12</v>
@@ -51759,7 +57369,7 @@
         <v>253</v>
       </c>
       <c r="D270" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E270" s="13">
         <v>12</v>
@@ -51783,7 +57393,7 @@
         <v>254</v>
       </c>
       <c r="D271" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E271" s="13">
         <v>12</v>
@@ -51831,7 +57441,7 @@
         <v>256</v>
       </c>
       <c r="D273" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E273" s="13">
         <v>12</v>
@@ -52143,7 +57753,7 @@
         <v>268</v>
       </c>
       <c r="D286" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E286" s="13">
         <v>12</v>
@@ -52215,7 +57825,7 @@
         <v>270</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E289" s="13">
         <v>12</v>
@@ -52239,7 +57849,7 @@
         <v>271</v>
       </c>
       <c r="D290" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E290" s="13">
         <v>12</v>
@@ -52383,7 +57993,7 @@
         <v>277</v>
       </c>
       <c r="D296" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E296" s="13">
         <v>12</v>
@@ -52935,7 +58545,7 @@
         <v>300</v>
       </c>
       <c r="D319" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E319" s="13">
         <v>12</v>
@@ -53127,7 +58737,7 @@
         <v>308</v>
       </c>
       <c r="D327" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E327" s="13">
         <v>12</v>
@@ -53391,7 +59001,7 @@
         <v>319</v>
       </c>
       <c r="D338" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E338" s="13">
         <v>12</v>
@@ -53487,7 +59097,7 @@
         <v>323</v>
       </c>
       <c r="D342" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E342" s="13">
         <v>12</v>
@@ -53679,7 +59289,7 @@
         <v>331</v>
       </c>
       <c r="D350" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E350" s="13">
         <v>12</v>
@@ -53919,7 +59529,7 @@
         <v>341</v>
       </c>
       <c r="D360" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E360" s="13">
         <v>12</v>
@@ -54015,7 +59625,7 @@
         <v>345</v>
       </c>
       <c r="D364" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E364" s="13">
         <v>12</v>
@@ -54039,7 +59649,7 @@
         <v>346</v>
       </c>
       <c r="D365" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E365" s="13">
         <v>12</v>
@@ -54063,7 +59673,7 @@
         <v>347</v>
       </c>
       <c r="D366" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E366" s="13">
         <v>12</v>
@@ -54159,7 +59769,7 @@
         <v>351</v>
       </c>
       <c r="D370" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E370" s="13">
         <v>12</v>
@@ -54255,7 +59865,7 @@
         <v>355</v>
       </c>
       <c r="D374" s="13" t="s">
-        <v>7</v>
+        <v>1047</v>
       </c>
       <c r="E374" s="13">
         <v>12</v>
@@ -54327,7 +59937,7 @@
         <v>357</v>
       </c>
       <c r="D377" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E377" s="13">
         <v>12</v>
@@ -54447,7 +60057,7 @@
         <v>362</v>
       </c>
       <c r="D382" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E382" s="13">
         <v>12</v>
@@ -54711,7 +60321,7 @@
         <v>373</v>
       </c>
       <c r="D393" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E393" s="13">
         <v>12</v>
@@ -54903,7 +60513,7 @@
         <v>381</v>
       </c>
       <c r="D401" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E401" s="13">
         <v>12</v>
@@ -55095,7 +60705,7 @@
         <v>389</v>
       </c>
       <c r="D409" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E409" s="13">
         <v>12</v>
@@ -55239,7 +60849,7 @@
         <v>395</v>
       </c>
       <c r="D415" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E415" s="13">
         <v>12</v>
@@ -55407,7 +61017,7 @@
         <v>402</v>
       </c>
       <c r="D422" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E422" s="13">
         <v>12</v>
@@ -55431,7 +61041,7 @@
         <v>403</v>
       </c>
       <c r="D423" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E423" s="13">
         <v>12</v>
@@ -55455,7 +61065,7 @@
         <v>404</v>
       </c>
       <c r="D424" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E424" s="13">
         <v>12</v>
@@ -55479,7 +61089,7 @@
         <v>405</v>
       </c>
       <c r="D425" s="13" t="s">
-        <v>7</v>
+        <v>1047</v>
       </c>
       <c r="E425" s="13">
         <v>12</v>
@@ -55647,7 +61257,7 @@
         <v>410</v>
       </c>
       <c r="D432" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E432" s="13">
         <v>12</v>
@@ -56055,7 +61665,7 @@
         <v>426</v>
       </c>
       <c r="D449" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E449" s="13">
         <v>12</v>
@@ -56103,7 +61713,7 @@
         <v>428</v>
       </c>
       <c r="D451" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E451" s="13">
         <v>12</v>
@@ -56295,7 +61905,7 @@
         <v>436</v>
       </c>
       <c r="D459" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E459" s="13">
         <v>12</v>
@@ -56319,7 +61929,7 @@
         <v>437</v>
       </c>
       <c r="D460" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E460" s="13">
         <v>12</v>
@@ -56391,7 +62001,7 @@
         <v>440</v>
       </c>
       <c r="D463" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E463" s="13">
         <v>12</v>
@@ -56535,7 +62145,7 @@
         <v>446</v>
       </c>
       <c r="D469" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E469" s="13">
         <v>12</v>
@@ -56583,7 +62193,7 @@
         <v>448</v>
       </c>
       <c r="D471" s="13" t="s">
-        <v>7</v>
+        <v>1047</v>
       </c>
       <c r="E471" s="13">
         <v>12</v>
@@ -56631,7 +62241,7 @@
         <v>450</v>
       </c>
       <c r="D473" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E473" s="13">
         <v>12</v>
@@ -57015,7 +62625,7 @@
         <v>466</v>
       </c>
       <c r="D489" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E489" s="13">
         <v>12</v>
@@ -57135,7 +62745,7 @@
         <v>470</v>
       </c>
       <c r="D494" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E494" s="13">
         <v>12</v>
@@ -57255,7 +62865,7 @@
         <v>475</v>
       </c>
       <c r="D499" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E499" s="13">
         <v>12</v>
@@ -57303,7 +62913,7 @@
         <v>477</v>
       </c>
       <c r="D501" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E501" s="13">
         <v>12</v>
@@ -57375,7 +62985,7 @@
         <v>480</v>
       </c>
       <c r="D504" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E504" s="13">
         <v>12</v>
@@ -57399,7 +63009,7 @@
         <v>481</v>
       </c>
       <c r="D505" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E505" s="13">
         <v>12</v>
@@ -57471,7 +63081,7 @@
         <v>484</v>
       </c>
       <c r="D508" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E508" s="13">
         <v>12</v>
@@ -57615,7 +63225,7 @@
         <v>489</v>
       </c>
       <c r="D514" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E514" s="13">
         <v>12</v>
@@ -57807,7 +63417,7 @@
         <v>497</v>
       </c>
       <c r="D522" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E522" s="13">
         <v>12</v>
@@ -57879,7 +63489,7 @@
         <v>500</v>
       </c>
       <c r="D525" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E525" s="13">
         <v>12</v>
@@ -57903,7 +63513,7 @@
         <v>501</v>
       </c>
       <c r="D526" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E526" s="13">
         <v>12</v>
@@ -58071,7 +63681,7 @@
         <v>507</v>
       </c>
       <c r="D533" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E533" s="13">
         <v>12</v>
@@ -58119,7 +63729,7 @@
         <v>508</v>
       </c>
       <c r="D535" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E535" s="13">
         <v>12</v>
@@ -58191,7 +63801,7 @@
         <v>511</v>
       </c>
       <c r="D538" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E538" s="13">
         <v>12</v>
@@ -58407,7 +64017,7 @@
         <v>520</v>
       </c>
       <c r="D547" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E547" s="13">
         <v>12</v>
@@ -58431,7 +64041,7 @@
         <v>521</v>
       </c>
       <c r="D548" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E548" s="13">
         <v>12</v>
@@ -58479,7 +64089,7 @@
         <v>523</v>
       </c>
       <c r="D550" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E550" s="13">
         <v>12</v>
@@ -58791,7 +64401,7 @@
         <v>536</v>
       </c>
       <c r="D563" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E563" s="13">
         <v>12</v>
@@ -58815,7 +64425,7 @@
         <v>537</v>
       </c>
       <c r="D564" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E564" s="13">
         <v>12</v>
@@ -58839,7 +64449,7 @@
         <v>538</v>
       </c>
       <c r="D565" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E565" s="13">
         <v>12</v>
@@ -59175,7 +64785,7 @@
         <v>549</v>
       </c>
       <c r="D579" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E579" s="13">
         <v>12</v>
@@ -59391,7 +65001,7 @@
         <v>558</v>
       </c>
       <c r="D588" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E588" s="13">
         <v>12</v>
@@ -59463,7 +65073,7 @@
         <v>560</v>
       </c>
       <c r="D591" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E591" s="13">
         <v>12</v>
@@ -59559,7 +65169,7 @@
         <v>564</v>
       </c>
       <c r="D595" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E595" s="13">
         <v>12</v>
@@ -59655,7 +65265,7 @@
         <v>568</v>
       </c>
       <c r="D599" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E599" s="13">
         <v>12</v>
@@ -59679,7 +65289,7 @@
         <v>569</v>
       </c>
       <c r="D600" s="13" t="s">
-        <v>7</v>
+        <v>1047</v>
       </c>
       <c r="E600" s="13">
         <v>12</v>
@@ -59775,7 +65385,7 @@
         <v>572</v>
       </c>
       <c r="D604" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E604" s="13">
         <v>12</v>
@@ -59823,7 +65433,7 @@
         <v>573</v>
       </c>
       <c r="D606" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E606" s="13">
         <v>12</v>
@@ -59871,7 +65481,7 @@
         <v>575</v>
       </c>
       <c r="D608" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E608" s="13">
         <v>12</v>
@@ -60087,7 +65697,7 @@
         <v>584</v>
       </c>
       <c r="D617" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E617" s="13">
         <v>12</v>
@@ -60207,7 +65817,7 @@
         <v>588</v>
       </c>
       <c r="D622" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E622" s="13">
         <v>12</v>
@@ -60375,7 +65985,7 @@
         <v>595</v>
       </c>
       <c r="D629" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E629" s="13">
         <v>12</v>
@@ -60399,7 +66009,7 @@
         <v>596</v>
       </c>
       <c r="D630" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E630" s="13">
         <v>12</v>
@@ -60471,7 +66081,7 @@
         <v>598</v>
       </c>
       <c r="D633" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E633" s="13">
         <v>12</v>
@@ -60807,7 +66417,7 @@
         <v>612</v>
       </c>
       <c r="D647" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E647" s="13">
         <v>12</v>
@@ -60951,7 +66561,7 @@
         <v>617</v>
       </c>
       <c r="D653" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E653" s="13">
         <v>12</v>
@@ -61071,7 +66681,7 @@
         <v>621</v>
       </c>
       <c r="D658" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E658" s="13">
         <v>12</v>
@@ -61311,7 +66921,7 @@
         <v>631</v>
       </c>
       <c r="D668" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E668" s="13">
         <v>12</v>
@@ -61359,7 +66969,7 @@
         <v>632</v>
       </c>
       <c r="D670" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E670" s="13">
         <v>12</v>
@@ -61767,7 +67377,7 @@
         <v>649</v>
       </c>
       <c r="D687" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E687" s="13">
         <v>12</v>
@@ -61791,7 +67401,7 @@
         <v>650</v>
       </c>
       <c r="D688" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E688" s="13">
         <v>12</v>
@@ -61911,7 +67521,7 @@
         <v>655</v>
       </c>
       <c r="D693" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E693" s="13">
         <v>12</v>
@@ -62127,7 +67737,7 @@
         <v>663</v>
       </c>
       <c r="D702" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E702" s="13">
         <v>12</v>
@@ -62151,7 +67761,7 @@
         <v>664</v>
       </c>
       <c r="D703" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E703" s="13">
         <v>12</v>
@@ -62439,7 +68049,7 @@
         <v>676</v>
       </c>
       <c r="D715" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E715" s="13">
         <v>12</v>
@@ -62583,7 +68193,7 @@
         <v>682</v>
       </c>
       <c r="D721" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E721" s="13">
         <v>12</v>
@@ -62607,7 +68217,7 @@
         <v>683</v>
       </c>
       <c r="D722" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E722" s="13">
         <v>12</v>
@@ -62655,7 +68265,7 @@
         <v>685</v>
       </c>
       <c r="D724" s="13" t="s">
-        <v>7</v>
+        <v>1043</v>
       </c>
       <c r="E724" s="13">
         <v>12</v>
@@ -62747,8 +68357,8 @@
       <c r="B728" s="13" t="s">
         <v>1012</v>
       </c>
-      <c r="C728" s="14" t="s">
-        <v>689</v>
+      <c r="C728" s="17" t="s">
+        <v>1044</v>
       </c>
       <c r="D728" s="13" t="s">
         <v>7</v>
@@ -62774,8 +68384,8 @@
       <c r="C729" s="14" t="s">
         <v>689</v>
       </c>
-      <c r="D729" s="13" t="s">
-        <v>7</v>
+      <c r="D729" s="17" t="s">
+        <v>1043</v>
       </c>
       <c r="E729" s="13">
         <v>12</v>

--- a/DPOPz DATABASE.xlsx
+++ b/DPOPz DATABASE.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subby/Downloads/dpoptionz-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27A862B-676C-EB40-A917-6AD4337511B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F63697-B6F2-EB4B-80C6-A85946AAB055}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51920" yWindow="620" windowWidth="19220" windowHeight="21000" activeTab="1" xr2:uid="{E04FA07E-3229-C048-A4EF-F04BD1865DFB}"/>
+    <workbookView xWindow="49240" yWindow="620" windowWidth="21900" windowHeight="21000" activeTab="1" xr2:uid="{E04FA07E-3229-C048-A4EF-F04BD1865DFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2078</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19926" uniqueCount="1423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20717" uniqueCount="2154">
   <si>
     <t>Timestamp</t>
   </si>
@@ -4928,6 +4929,2201 @@
   </si>
   <si>
     <t>A</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>op.31 叙情 [A]</t>
+  </si>
+  <si>
+    <t>Kailua [A]</t>
+  </si>
+  <si>
+    <t>The Onlyonez [A]</t>
+  </si>
+  <si>
+    <t>Colors (radio edit) [A]</t>
+  </si>
+  <si>
+    <t>Spica [A]</t>
+  </si>
+  <si>
+    <t>FAKE TIME [H]</t>
+  </si>
+  <si>
+    <t>RED ZONE [L]</t>
+  </si>
+  <si>
+    <t>MINT [A]</t>
+  </si>
+  <si>
+    <t>Candy Galy [A]</t>
+  </si>
+  <si>
+    <t>Fascination MAXX [A]</t>
+  </si>
+  <si>
+    <t>oratio [A]</t>
+  </si>
+  <si>
+    <t>Go Beyond!! [A]</t>
+  </si>
+  <si>
+    <t>Red. by Full Metal Jacket [A]</t>
+  </si>
+  <si>
+    <t>Liberation [A]</t>
+  </si>
+  <si>
+    <t>rumrum triplets [A]</t>
+  </si>
+  <si>
+    <t>BRAINSTORM [A]</t>
+  </si>
+  <si>
+    <t>夏色DIARY - L.E.D.-G STYLE MIX - [A]</t>
+  </si>
+  <si>
+    <t>NINJA IS DEAD IIDX ver. [A]</t>
+  </si>
+  <si>
+    <t>紫陽花 -AZISAI- [A]</t>
+  </si>
+  <si>
+    <t>九尾狐夜行 [A]</t>
+  </si>
+  <si>
+    <t>Afterimage d'automne [A]</t>
+  </si>
+  <si>
+    <t>Primitive Vibes [A]</t>
+  </si>
+  <si>
+    <t>Fire Beat [A]</t>
+  </si>
+  <si>
+    <t>Pārvatī [A]</t>
+  </si>
+  <si>
+    <t>CUE CUE RESCUE [L]</t>
+  </si>
+  <si>
+    <t>《PL|RAYER》 [A]</t>
+  </si>
+  <si>
+    <t>Sword of Vengeance [A]</t>
+  </si>
+  <si>
+    <t>灼熱 Lost Summer Dayz [A]</t>
+  </si>
+  <si>
+    <t>era (nostalmix) [H]</t>
+  </si>
+  <si>
+    <t>Summer Vacation(CU mix) [H]</t>
+  </si>
+  <si>
+    <t>route 80s [A]</t>
+  </si>
+  <si>
+    <t>stoic [A]</t>
+  </si>
+  <si>
+    <t>murmur twins [A]</t>
+  </si>
+  <si>
+    <t>GHOST REVIVAL [A]</t>
+  </si>
+  <si>
+    <t>SCREAM SQUAD [A]</t>
+  </si>
+  <si>
+    <t>Concertino in Blue [A]</t>
+  </si>
+  <si>
+    <t>Ganymede [A]</t>
+  </si>
+  <si>
+    <t>smile [A]</t>
+  </si>
+  <si>
+    <t>snow storm [A]</t>
+  </si>
+  <si>
+    <t>Anisakis -somatic mutation type"Forza"- [A]</t>
+  </si>
+  <si>
+    <t>TROOPERS [A]</t>
+  </si>
+  <si>
+    <t>3y3s [A]</t>
+  </si>
+  <si>
+    <t>ミッドナイト堕天使 (SINO) [A]</t>
+  </si>
+  <si>
+    <t>凛として咲く花の如く [L]</t>
+  </si>
+  <si>
+    <t>Evans [A]</t>
+  </si>
+  <si>
+    <t>Broken [A]</t>
+  </si>
+  <si>
+    <t>Session 9 -Chronicles- [A]</t>
+  </si>
+  <si>
+    <t>SPECIAL SUMMER CAMPAIGN! [A]</t>
+  </si>
+  <si>
+    <t>yellow head joe [A]</t>
+  </si>
+  <si>
+    <t>子供の落書き帳 [A]</t>
+  </si>
+  <si>
+    <t>恋する☆宇宙戦争っ！！ [A]</t>
+  </si>
+  <si>
+    <t>Little Star [A]</t>
+  </si>
+  <si>
+    <t>トリカゴノ鳳凰 [A]</t>
+  </si>
+  <si>
+    <t>即席！脳直★ミュージックシステム [A]</t>
+  </si>
+  <si>
+    <t>Elektrick U-Phoria [A]</t>
+  </si>
+  <si>
+    <t>The Least 100sec [A]</t>
+  </si>
+  <si>
+    <t>We're so Happy (P*Light Remix) IIDX ver. [A]</t>
+  </si>
+  <si>
+    <t>ZZ [A]</t>
+  </si>
+  <si>
+    <t>199024club -Re:BounceKiller- [A]</t>
+  </si>
+  <si>
+    <t>Battle Train -IIDX Edition- [A]</t>
+  </si>
+  <si>
+    <t>Highcharge Divolt [A]</t>
+  </si>
+  <si>
+    <t>HADES [A]</t>
+  </si>
+  <si>
+    <t>Rave Cannon [A]</t>
+  </si>
+  <si>
+    <t>TOGAKUSHI [A]</t>
+  </si>
+  <si>
+    <t>焱影 [A]</t>
+  </si>
+  <si>
+    <t>童話回廊 [A]</t>
+  </si>
+  <si>
+    <t>Antigravity [A]</t>
+  </si>
+  <si>
+    <t>Eine Haube ～聖地の果てにあるもの～ [A]</t>
+  </si>
+  <si>
+    <t>encounter [A]</t>
+  </si>
+  <si>
+    <t>Persephone [A]</t>
+  </si>
+  <si>
+    <t>Raspberry Railgun [A]</t>
+  </si>
+  <si>
+    <t>Carry Me Away [A]</t>
+  </si>
+  <si>
+    <t>GENE [L]</t>
+  </si>
+  <si>
+    <t>深淵に捧ぐレクイエム [A]</t>
+  </si>
+  <si>
+    <t>Rubrum Piano [A]</t>
+  </si>
+  <si>
+    <t>バッド・スイーツ、バッド・ドリーム [A]</t>
+  </si>
+  <si>
+    <t>雪上断火 [A]</t>
+  </si>
+  <si>
+    <t>#CMFLG [A]</t>
+  </si>
+  <si>
+    <t>Meissa [A]</t>
+  </si>
+  <si>
+    <t>ACTØ [A]</t>
+  </si>
+  <si>
+    <t>CODE:2 [A]</t>
+  </si>
+  <si>
+    <t>Sirius [A]</t>
+  </si>
+  <si>
+    <t>残像ニ繋ガレタ追憶ノHIDEAWAY [A]</t>
+  </si>
+  <si>
+    <t>電光 [A]</t>
+  </si>
+  <si>
+    <t>Here We Go Now [A]</t>
+  </si>
+  <si>
+    <t>スパークリング☆彡ハイパーチューン！！ [A]</t>
+  </si>
+  <si>
+    <t>RALLY '25 [A]</t>
+  </si>
+  <si>
+    <t>era (nostalmix) [A]</t>
+  </si>
+  <si>
+    <t>era (step mix) [A]</t>
+  </si>
+  <si>
+    <t>starmine [A]</t>
+  </si>
+  <si>
+    <t>QQQ [H]</t>
+  </si>
+  <si>
+    <t>革命 [H]</t>
+  </si>
+  <si>
+    <t>桜 [A]</t>
+  </si>
+  <si>
+    <t>lower world [A]</t>
+  </si>
+  <si>
+    <t>1st Samurai [A]</t>
+  </si>
+  <si>
+    <t>gigadelic [H]</t>
+  </si>
+  <si>
+    <t>BLOCKS [A]</t>
+  </si>
+  <si>
+    <t>POODLE [L]</t>
+  </si>
+  <si>
+    <t>華蝶風雪 [A]</t>
+  </si>
+  <si>
+    <t>Sense 2007 [H]</t>
+  </si>
+  <si>
+    <t>INORI [A]</t>
+  </si>
+  <si>
+    <t>KAMAITACHI [A]</t>
+  </si>
+  <si>
+    <t>Be OK [A]</t>
+  </si>
+  <si>
+    <t>Do it!! Do it!! (EMP) [A]</t>
+  </si>
+  <si>
+    <t>ミラージュ・レジデンス [A]</t>
+  </si>
+  <si>
+    <t>Punch Love♡仮面 [L]</t>
+  </si>
+  <si>
+    <t>DOMINION [A]</t>
+  </si>
+  <si>
+    <t>GALGALIM [A]</t>
+  </si>
+  <si>
+    <t>GOLDEN CROSS [A]</t>
+  </si>
+  <si>
+    <t>New Castle Legions (ROOT) [A]</t>
+  </si>
+  <si>
+    <t>SABER WING [A]</t>
+  </si>
+  <si>
+    <t>sakura storm [A]</t>
+  </si>
+  <si>
+    <t>THE BLACK KNIGHT [A]</t>
+  </si>
+  <si>
+    <t>旅人リラン [A]</t>
+  </si>
+  <si>
+    <t>黒髪乱れし修羅となりて [A]</t>
+  </si>
+  <si>
+    <t>ƒƒƒƒƒ [A]</t>
+  </si>
+  <si>
+    <t>Infinite cave [A]</t>
+  </si>
+  <si>
+    <t>GIGANT [L]</t>
+  </si>
+  <si>
+    <t>FLOWER [A]</t>
+  </si>
+  <si>
+    <t>True Blue [A]</t>
+  </si>
+  <si>
+    <t>ΕΛΠΙΣ [A]</t>
+  </si>
+  <si>
+    <t>カジノファイヤーことみちゃん [A]</t>
+  </si>
+  <si>
+    <t>狂イ咲ケ焔ノ華 [A]</t>
+  </si>
+  <si>
+    <t>Close the World feat.a☆ru [A]</t>
+  </si>
+  <si>
+    <t>rainbow guitar weeps [A]</t>
+  </si>
+  <si>
+    <t>Unicorn tail [A]</t>
+  </si>
+  <si>
+    <t>ÆTHER [L]</t>
+  </si>
+  <si>
+    <t>BRAVE OUT [L]</t>
+  </si>
+  <si>
+    <t>Gravigazer [A]</t>
+  </si>
+  <si>
+    <t>Invitation from Mr.C [A]</t>
+  </si>
+  <si>
+    <t>Rave*it!! Rave*it!! [A]</t>
+  </si>
+  <si>
+    <t>Ｘ↑Ｘ↓ [A]</t>
+  </si>
+  <si>
+    <t>chaos eater -IIDX edition- [A]</t>
+  </si>
+  <si>
+    <t>BabeL ～Grand Story～ [A]</t>
+  </si>
+  <si>
+    <t>FUZIN RIZIN [A]</t>
+  </si>
+  <si>
+    <t>Summerlights(IIDX Edition) [A]</t>
+  </si>
+  <si>
+    <t>Arca [A]</t>
+  </si>
+  <si>
+    <t>Papilio ulysses [A]</t>
+  </si>
+  <si>
+    <t>Drastic Dramatic [A]</t>
+  </si>
+  <si>
+    <t>GENE [A]</t>
+  </si>
+  <si>
+    <t>Mächö Mönky [A]</t>
+  </si>
+  <si>
+    <t>Night! Night! Night! [A]</t>
+  </si>
+  <si>
+    <t>ONIGOROSHI [A]</t>
+  </si>
+  <si>
+    <t>泰東ノ翠霞 (ROOT) [A]</t>
+  </si>
+  <si>
+    <t>AKASHIC BREAK [A]</t>
+  </si>
+  <si>
+    <t>Rave Patroller [A]</t>
+  </si>
+  <si>
+    <t>T-REX vs Velociraptor (In the Far east euphoria) [A]</t>
+  </si>
+  <si>
+    <t>BIGソムタム [A]</t>
+  </si>
+  <si>
+    <t>Dawn Saga [A]</t>
+  </si>
+  <si>
+    <t>OTOKOZAKA [A]</t>
+  </si>
+  <si>
+    <t>Vitrum [A]</t>
+  </si>
+  <si>
+    <t>スーパー戦湯ババンバーン [A]</t>
+  </si>
+  <si>
+    <t>One for All [A]</t>
+  </si>
+  <si>
+    <t>禊 [A]</t>
+  </si>
+  <si>
+    <t>ONE AND ONLY [A]</t>
+  </si>
+  <si>
+    <t>Dahlia [A]</t>
+  </si>
+  <si>
+    <t>JUSTICE/GUILTY feat. Nana Takahashi &amp; 709sec. [A]</t>
+  </si>
+  <si>
+    <t>T.R.O.L.L. [A]</t>
+  </si>
+  <si>
+    <t>Mid-Corner (Magic Maker) [A]</t>
+  </si>
+  <si>
+    <t>SISYPHUS [A]</t>
+  </si>
+  <si>
+    <t>Makin' It [A]</t>
+  </si>
+  <si>
+    <t>RUGGED ASH [L]</t>
+  </si>
+  <si>
+    <t>DXY! [H]</t>
+  </si>
+  <si>
+    <t>SWEET LAB [A]</t>
+  </si>
+  <si>
+    <t>one or eight [L]</t>
+  </si>
+  <si>
+    <t>Innocent Walls [A]</t>
+  </si>
+  <si>
+    <t>Love Is Eternity [A]</t>
+  </si>
+  <si>
+    <t>No.13 [A]</t>
+  </si>
+  <si>
+    <t>FAKE TIME [A]</t>
+  </si>
+  <si>
+    <t>gigadelic [A]</t>
+  </si>
+  <si>
+    <t>garden [A]</t>
+  </si>
+  <si>
+    <t>Scripted Connection⇒ H mix [L]</t>
+  </si>
+  <si>
+    <t>CONTRACT [A]</t>
+  </si>
+  <si>
+    <t>tripping contact(teranoid&amp;MC Natsack Remix) [A]</t>
+  </si>
+  <si>
+    <t>Ganymede [L]</t>
+  </si>
+  <si>
+    <t>Sense 2007 [A]</t>
+  </si>
+  <si>
+    <t>TRANOID [A]</t>
+  </si>
+  <si>
+    <t>GRID KNIGHT [L]</t>
+  </si>
+  <si>
+    <t>the trigger of innocence [L]</t>
+  </si>
+  <si>
+    <t>Wanna Party? [L]</t>
+  </si>
+  <si>
+    <t>Colorful Cookie [A]</t>
+  </si>
+  <si>
+    <t>Kung-fu Empire [L]</t>
+  </si>
+  <si>
+    <t>eRAseRmOToRpHAntOM [A]</t>
+  </si>
+  <si>
+    <t>BLACK.by X-Cross Fade [A]</t>
+  </si>
+  <si>
+    <t>NNRT [A]</t>
+  </si>
+  <si>
+    <t>Snake Stick [A]</t>
+  </si>
+  <si>
+    <t>WONDER WALKER [A]</t>
+  </si>
+  <si>
+    <t>A MINSTREL ～ ver. short-scape ～ [L]</t>
+  </si>
+  <si>
+    <t>DAY DREAM [A]</t>
+  </si>
+  <si>
+    <t>Hollywood Galaxy [A]</t>
+  </si>
+  <si>
+    <t>JOMANDA [A]</t>
+  </si>
+  <si>
+    <t>SYNC-ANTHEM [A]</t>
+  </si>
+  <si>
+    <t>音楽 [A]</t>
+  </si>
+  <si>
+    <t>Time to Empress [L]</t>
+  </si>
+  <si>
+    <t>Adularia [A]</t>
+  </si>
+  <si>
+    <t>I will be back -オレは帰ってきた- [A]</t>
+  </si>
+  <si>
+    <t>INSOMNIA [A]</t>
+  </si>
+  <si>
+    <t>PUNISHER [A]</t>
+  </si>
+  <si>
+    <t>RIZING YOU UP [A]</t>
+  </si>
+  <si>
+    <t>轟け！恋のビーンボール！！ [A]</t>
+  </si>
+  <si>
+    <t>BLUE DRAGON(雷龍RemixIIDX) [L]</t>
+  </si>
+  <si>
+    <t>Feel The Beat [L]</t>
+  </si>
+  <si>
+    <t>cinder [A]</t>
+  </si>
+  <si>
+    <t>Shooting Fireball [A]</t>
+  </si>
+  <si>
+    <t>Sounds Of Summer [A]</t>
+  </si>
+  <si>
+    <t>SpaceLand☆TOYBOX [A]</t>
+  </si>
+  <si>
+    <t>鬼天 [A]</t>
+  </si>
+  <si>
+    <t>Devil's Gear [A]</t>
+  </si>
+  <si>
+    <t>Nightmare before oversleep [A]</t>
+  </si>
+  <si>
+    <t>Super Rush [A]</t>
+  </si>
+  <si>
+    <t>〆 [A]</t>
+  </si>
+  <si>
+    <t>刃図羅 [A]</t>
+  </si>
+  <si>
+    <t>Umbral [L]</t>
+  </si>
+  <si>
+    <t>255 [A]</t>
+  </si>
+  <si>
+    <t>The Chase [A]</t>
+  </si>
+  <si>
+    <t>Xperanza [A]</t>
+  </si>
+  <si>
+    <t>EVANESCENT [A]</t>
+  </si>
+  <si>
+    <t>GIGA THRASH [A]</t>
+  </si>
+  <si>
+    <t>L.F.O [A]</t>
+  </si>
+  <si>
+    <t>Trill auf G [A]</t>
+  </si>
+  <si>
+    <t>Double Dribble [A]</t>
+  </si>
+  <si>
+    <t>Friction[!]Function [A]</t>
+  </si>
+  <si>
+    <t>Megalara Garuda [A]</t>
+  </si>
+  <si>
+    <t>TRIUMPH [A]</t>
+  </si>
+  <si>
+    <t>Ypsilon [L]</t>
+  </si>
+  <si>
+    <t>GiGaGaHell [A]</t>
+  </si>
+  <si>
+    <t>グッバイ宣言 [L]</t>
+  </si>
+  <si>
+    <t>ハイテックトキオ [L]</t>
+  </si>
+  <si>
+    <t>Always We Trust In You [A]</t>
+  </si>
+  <si>
+    <t>dica dica [A]</t>
+  </si>
+  <si>
+    <t>glacia [A]</t>
+  </si>
+  <si>
+    <t>Hat Surprise (Season 2) [A]</t>
+  </si>
+  <si>
+    <t>MAX 360 [A]</t>
+  </si>
+  <si>
+    <t>Peaktime Booster [A]</t>
+  </si>
+  <si>
+    <t>Super Freak [A]</t>
+  </si>
+  <si>
+    <t>神のシナリオ [A]</t>
+  </si>
+  <si>
+    <t>KING [L]</t>
+  </si>
+  <si>
+    <t>神っぽいな [L]</t>
+  </si>
+  <si>
+    <t>GAME ON [A]</t>
+  </si>
+  <si>
+    <t>Ghost Pulse [A]</t>
+  </si>
+  <si>
+    <t>Seven Times Four [A]</t>
+  </si>
+  <si>
+    <t>今宵、ロマンス横丁。 [A]</t>
+  </si>
+  <si>
+    <t>灼熱Beach Side Bunny (かめりあ's "Summertime D'n'B" Remix) [A]</t>
+  </si>
+  <si>
+    <t>終焔のClaudia [A]</t>
+  </si>
+  <si>
+    <t>Bring The Fire [A]</t>
+  </si>
+  <si>
+    <t>Satellite Burst [A]</t>
+  </si>
+  <si>
+    <t>u gotta beat [A]</t>
+  </si>
+  <si>
+    <t>Plazma [L]</t>
+  </si>
+  <si>
+    <t>Disco Killer Music Lover [A]</t>
+  </si>
+  <si>
+    <t>King of Tribe [A]</t>
+  </si>
+  <si>
+    <t>G2 [A]</t>
+  </si>
+  <si>
+    <t>MAX 300 [A]</t>
+  </si>
+  <si>
+    <t>革命 [A]</t>
+  </si>
+  <si>
+    <t>RISLIM -Remix- [A]</t>
+  </si>
+  <si>
+    <t>雪月花 [A]</t>
+  </si>
+  <si>
+    <t>GENOCIDE [H]</t>
+  </si>
+  <si>
+    <t>AA [A]</t>
+  </si>
+  <si>
+    <t>Sphere [A]</t>
+  </si>
+  <si>
+    <t>INAZUMA [A]</t>
+  </si>
+  <si>
+    <t>華蝶風雪 [L]</t>
+  </si>
+  <si>
+    <t>LASER CRUSTER [A]</t>
+  </si>
+  <si>
+    <t>電人、暁に斃れる。 [A]</t>
+  </si>
+  <si>
+    <t>ICARUS [A]</t>
+  </si>
+  <si>
+    <t>satellite020712 from "CODED ARMS" (DJT) [A]</t>
+  </si>
+  <si>
+    <t>State Of The Art (SINO) [A]</t>
+  </si>
+  <si>
+    <t>NEW GENERATION -もう、お前しか見えない- [L]</t>
+  </si>
+  <si>
+    <t>Arabian Rave Night [L]</t>
+  </si>
+  <si>
+    <t>B4U(BEMANI FOR YOU MIX) [L]</t>
+  </si>
+  <si>
+    <t>EXUSIA [A]</t>
+  </si>
+  <si>
+    <t>G59 [A]</t>
+  </si>
+  <si>
+    <t>Dances with Snow Fairies [A]</t>
+  </si>
+  <si>
+    <t>ZETA～素数の世界と超越者～ [A]</t>
+  </si>
+  <si>
+    <t>F [A]</t>
+  </si>
+  <si>
+    <t>HAERETICUS [A]</t>
+  </si>
+  <si>
+    <t>KYAMISAMA ONEGAI! [L]</t>
+  </si>
+  <si>
+    <t>Devilz Staircase [A]</t>
+  </si>
+  <si>
+    <t>GAIA [A]</t>
+  </si>
+  <si>
+    <t>Plan 8 [A]</t>
+  </si>
+  <si>
+    <t>Sol Cosine Job 2 [A]</t>
+  </si>
+  <si>
+    <t>アストライアの双皿 [A]</t>
+  </si>
+  <si>
+    <t>シュレーディンガーの猫 [A]</t>
+  </si>
+  <si>
+    <t>たまゆら [A]</t>
+  </si>
+  <si>
+    <t>仮想空間の旅人たち [L]</t>
+  </si>
+  <si>
+    <t>龍と少女とデコヒーレンス [L]</t>
+  </si>
+  <si>
+    <t>Ancient Scapes [A]</t>
+  </si>
+  <si>
+    <t>DARK LEGACY [A]</t>
+  </si>
+  <si>
+    <t>invoker [A]</t>
+  </si>
+  <si>
+    <t>Last Dance [A]</t>
+  </si>
+  <si>
+    <t>バンブーソード・ガール [A]</t>
+  </si>
+  <si>
+    <t>海神 [A]</t>
+  </si>
+  <si>
+    <t>Miracle 5ympho X [L]</t>
+  </si>
+  <si>
+    <t>Broken Sword [A]</t>
+  </si>
+  <si>
+    <t>Despair of ELFERIA [A]</t>
+  </si>
+  <si>
+    <t>Night sky [A]</t>
+  </si>
+  <si>
+    <t>TIEFSEE [A]</t>
+  </si>
+  <si>
+    <t>それは花火のような恋 [A]</t>
+  </si>
+  <si>
+    <t>リリーゼと炎龍レーヴァテイン [A]</t>
+  </si>
+  <si>
+    <t>千年ノ理 [A]</t>
+  </si>
+  <si>
+    <t>超青少年ノ為ノ超多幸ナ超古典的超舞曲 [A]</t>
+  </si>
+  <si>
+    <t>Beat Radiance [L]</t>
+  </si>
+  <si>
+    <t>GUILTY [L]</t>
+  </si>
+  <si>
+    <t>AO-1 [A]</t>
+  </si>
+  <si>
+    <t>Blue Spring Express [A]</t>
+  </si>
+  <si>
+    <t>Godspeed [A]</t>
+  </si>
+  <si>
+    <t>StrayedCatz [A]</t>
+  </si>
+  <si>
+    <t>Caterpillar [A]</t>
+  </si>
+  <si>
+    <t>DORNWALD ～Junge～ [A]</t>
+  </si>
+  <si>
+    <t>Quakes [A]</t>
+  </si>
+  <si>
+    <t>RAIN [A]</t>
+  </si>
+  <si>
+    <t>Snakey Kung-fu [A]</t>
+  </si>
+  <si>
+    <t>Amazing Mirage [L]</t>
+  </si>
+  <si>
+    <t>AA -rebuild- [A]</t>
+  </si>
+  <si>
+    <t>ANCHOR [A]</t>
+  </si>
+  <si>
+    <t>DEADHEAT [A]</t>
+  </si>
+  <si>
+    <t>Illusionary Waterlily [A]</t>
+  </si>
+  <si>
+    <t>NITROUS CANNON [A]</t>
+  </si>
+  <si>
+    <t>Rampage [A]</t>
+  </si>
+  <si>
+    <t>Slipstream [A]</t>
+  </si>
+  <si>
+    <t>神謳 -RESONANCE- [A]</t>
+  </si>
+  <si>
+    <t>Catch Our Fire! [A]</t>
+  </si>
+  <si>
+    <t>GO OVER WITH GLARE -ROOTAGE 26- [A]</t>
+  </si>
+  <si>
+    <t>HARD BRAIN [A]</t>
+  </si>
+  <si>
+    <t>KILL EACH OTHER [A]</t>
+  </si>
+  <si>
+    <t>Lethal Weapon [A]</t>
+  </si>
+  <si>
+    <t>Red. by Jack Trance [A]</t>
+  </si>
+  <si>
+    <t>ruin of opals [A]</t>
+  </si>
+  <si>
+    <t>THE DAY OF JUBILATIONS [A]</t>
+  </si>
+  <si>
+    <t>Visterhv [A]</t>
+  </si>
+  <si>
+    <t>voltississimo [A]</t>
+  </si>
+  <si>
+    <t>抱きしめてモナムール [A]</t>
+  </si>
+  <si>
+    <t>金野火織の金色提言 [A]</t>
+  </si>
+  <si>
+    <t>Dans la nuit de l'éternité [A]</t>
+  </si>
+  <si>
+    <t>LASER CRUSTER (IGNITE REMIX) [A]</t>
+  </si>
+  <si>
+    <t>LIGHTNING STRIKES [A]</t>
+  </si>
+  <si>
+    <t>Lords Of The Roundtable [A]</t>
+  </si>
+  <si>
+    <t>Matt Silver [A]</t>
+  </si>
+  <si>
+    <t>SCREW // owo // SCREW [A]</t>
+  </si>
+  <si>
+    <t>TECHNO Style Essentials [A]</t>
+  </si>
+  <si>
+    <t>Vinculum stellarum [A]</t>
+  </si>
+  <si>
+    <t>華麗なる大犬円舞曲 [A]</t>
+  </si>
+  <si>
+    <t>ASIAN VIRTUAL REALITIES (MELTING TOGETHER IN DAZZLING DARKNESS) [A]</t>
+  </si>
+  <si>
+    <t>Empire of Fury [A]</t>
+  </si>
+  <si>
+    <t>innocent revolver [A]</t>
+  </si>
+  <si>
+    <t>SOLID STATE SQUAD -RISEN RELIC REMIX- [A]</t>
+  </si>
+  <si>
+    <t>Tiempo Loco [A]</t>
+  </si>
+  <si>
+    <t>世界の果てに約束の凱歌を -ReUnion- [A]</t>
+  </si>
+  <si>
+    <t>水鏡の異界 [A]</t>
+  </si>
+  <si>
+    <t>魔法のかくれんぼ [A]</t>
+  </si>
+  <si>
+    <t>Burning Flame [L]</t>
+  </si>
+  <si>
+    <t>POLꓘAMAИIA [L]</t>
+  </si>
+  <si>
+    <t>新宝島 [L]</t>
+  </si>
+  <si>
+    <t>Aftermath [A]</t>
+  </si>
+  <si>
+    <t>ALTERNATOR [A]</t>
+  </si>
+  <si>
+    <t>Angel's Ladder [A]</t>
+  </si>
+  <si>
+    <t>Don't believe the hype [A]</t>
+  </si>
+  <si>
+    <t>Fegrix [A]</t>
+  </si>
+  <si>
+    <t>LIVE DRIVING!! feat. 花たん [A]</t>
+  </si>
+  <si>
+    <t>Purple Perplex [A]</t>
+  </si>
+  <si>
+    <t>Push on Beats!～音ゲの国のeX-ストリーマー～ [A]</t>
+  </si>
+  <si>
+    <t>Smalt #28598F [A]</t>
+  </si>
+  <si>
+    <t>TOMAHAWK [A]</t>
+  </si>
+  <si>
+    <t>Triple Cross [A]</t>
+  </si>
+  <si>
+    <t>烽火連天の刃 [A]</t>
+  </si>
+  <si>
+    <t>24h Endurance Race [A]</t>
+  </si>
+  <si>
+    <t>B.O.D.Y. [A]</t>
+  </si>
+  <si>
+    <t>BIGWAVERS [A]</t>
+  </si>
+  <si>
+    <t>I [A]</t>
+  </si>
+  <si>
+    <t>kors k's How to make OTOGE CORE 「LONG」 [A]</t>
+  </si>
+  <si>
+    <t>No Border [A]</t>
+  </si>
+  <si>
+    <t>Ōu Legends [A]</t>
+  </si>
+  <si>
+    <t>Stylus [A]</t>
+  </si>
+  <si>
+    <t>TECHNOPHOBIA [A]</t>
+  </si>
+  <si>
+    <t>ぞうしょく！？マイデンティティ [A]</t>
+  </si>
+  <si>
+    <t>恋愛＝精度×認識力 [A]</t>
+  </si>
+  <si>
+    <t>BLAZING_LAZER [A]</t>
+  </si>
+  <si>
+    <t>Cult Invitation [A]</t>
+  </si>
+  <si>
+    <t>frequent [A]</t>
+  </si>
+  <si>
+    <t>MAXIMUM CHEAT GIRL [A]</t>
+  </si>
+  <si>
+    <t>Out of Control [A]</t>
+  </si>
+  <si>
+    <t>Resonant [A]</t>
+  </si>
+  <si>
+    <t>Stereo Beasts [A]</t>
+  </si>
+  <si>
+    <t>Vermilion Carol [A]</t>
+  </si>
+  <si>
+    <t>Xb10r [A]</t>
+  </si>
+  <si>
+    <t>未完成ノ蒸氣驅動乙女 [A]</t>
+  </si>
+  <si>
+    <t>電腦都市 [A]</t>
+  </si>
+  <si>
+    <t>フォニイ [L]</t>
+  </si>
+  <si>
+    <t>1116 [A]</t>
+  </si>
+  <si>
+    <t>Aqvion [A]</t>
+  </si>
+  <si>
+    <t>COSMIC V3LOCITY [A]</t>
+  </si>
+  <si>
+    <t>DIVINE JUDGEMENT [A]</t>
+  </si>
+  <si>
+    <t>EX-MASSIVE FIGHTER [A]</t>
+  </si>
+  <si>
+    <t>EYE OF THE HEAVEN [A]</t>
+  </si>
+  <si>
+    <t>Pinky Happy Crazy [A]</t>
+  </si>
+  <si>
+    <t>Roar of Chronos [A]</t>
+  </si>
+  <si>
+    <t>Begin [A]</t>
+  </si>
+  <si>
+    <t>BitRacer [A]</t>
+  </si>
+  <si>
+    <t>From Human Blood [A]</t>
+  </si>
+  <si>
+    <t>HyperTwist [A]</t>
+  </si>
+  <si>
+    <t>Lisa-RICCIA [A]</t>
+  </si>
+  <si>
+    <t>Regina vespaE [A]</t>
+  </si>
+  <si>
+    <t>Space Battleship S4TØ [A]</t>
+  </si>
+  <si>
+    <t>UNDO THE NIGHT [A]</t>
+  </si>
+  <si>
+    <t>クレッシェンド [A]</t>
+  </si>
+  <si>
+    <t>ビビッド ☆＋＊。キラキライム [A]</t>
+  </si>
+  <si>
+    <t>ベンガル vs. アムール Battle [A]</t>
+  </si>
+  <si>
+    <t>ラブコメトキドキシリアス [A]</t>
+  </si>
+  <si>
+    <t>Holic [A]</t>
+  </si>
+  <si>
+    <t>A [A]</t>
+  </si>
+  <si>
+    <t>Cheer Train [A]</t>
+  </si>
+  <si>
+    <t>LAB [L]</t>
+  </si>
+  <si>
+    <t>Karma [A]</t>
+  </si>
+  <si>
+    <t>moon_child [A]</t>
+  </si>
+  <si>
+    <t>One More Lovely [A]</t>
+  </si>
+  <si>
+    <t>CaptivAte～浄化～ [L]</t>
+  </si>
+  <si>
+    <t>garden [L]</t>
+  </si>
+  <si>
+    <t>rage against usual [L]</t>
+  </si>
+  <si>
+    <t>Scripted Connection⇒ A mix [L]</t>
+  </si>
+  <si>
+    <t>Twelfth Style [L]</t>
+  </si>
+  <si>
+    <t>カゴノトリ～弐式～ [A]</t>
+  </si>
+  <si>
+    <t>VANESSA [A]</t>
+  </si>
+  <si>
+    <t>Candy Galy [L]</t>
+  </si>
+  <si>
+    <t>four pieces of heaven [A]</t>
+  </si>
+  <si>
+    <t>少年A [A]</t>
+  </si>
+  <si>
+    <t>THE DEEP STRIKER [L]</t>
+  </si>
+  <si>
+    <t>Übertreffen [L]</t>
+  </si>
+  <si>
+    <t>華爛漫 -Flowers- [L]</t>
+  </si>
+  <si>
+    <t>Y&amp;Co. is dead or alive (CB) [A]</t>
+  </si>
+  <si>
+    <t>Secrets [L]</t>
+  </si>
+  <si>
+    <t>thunder HOUSE NATION Remix [L]</t>
+  </si>
+  <si>
+    <t>Raison d'être～交差する宿命～ [A]</t>
+  </si>
+  <si>
+    <t>SOLID STATE SQUAD [A]</t>
+  </si>
+  <si>
+    <t>AIR RAID FROM THA UNDAGROUND [L]</t>
+  </si>
+  <si>
+    <t>灼熱Beach Side Bunny [A]</t>
+  </si>
+  <si>
+    <t>quaver♪ [A]</t>
+  </si>
+  <si>
+    <t>The Sampling Paradise [A]</t>
+  </si>
+  <si>
+    <t>Todestrieb [A]</t>
+  </si>
+  <si>
+    <t>YAKSHA [A]</t>
+  </si>
+  <si>
+    <t>聖人の塔 [A]</t>
+  </si>
+  <si>
+    <t>恋する☆宇宙戦争っ！！ [L]</t>
+  </si>
+  <si>
+    <t>neu [A]</t>
+  </si>
+  <si>
+    <t>Proof of the existence [A]</t>
+  </si>
+  <si>
+    <t>Timepiece phase II [A]</t>
+  </si>
+  <si>
+    <t>Timepiece phase II (CN Ver.) [A]</t>
+  </si>
+  <si>
+    <t>Valanga [A]</t>
+  </si>
+  <si>
+    <t>Zirkfied [A]</t>
+  </si>
+  <si>
+    <t>キャトられ♥恋はモ～モク [A]</t>
+  </si>
+  <si>
+    <t>ΕΛΠΙΣ [L]</t>
+  </si>
+  <si>
+    <t>Idola [A]</t>
+  </si>
+  <si>
+    <t>Verflucht [A]</t>
+  </si>
+  <si>
+    <t>旋律のドグマ～Misérables～ [A]</t>
+  </si>
+  <si>
+    <t>疾風迅雷 [A]</t>
+  </si>
+  <si>
+    <t>ALBA -黎明- [L]</t>
+  </si>
+  <si>
+    <t>Close the World feat.a☆ru [L]</t>
+  </si>
+  <si>
+    <t>invoker [L]</t>
+  </si>
+  <si>
+    <t>廿 [L]</t>
+  </si>
+  <si>
+    <t>海神 [L]</t>
+  </si>
+  <si>
+    <t>EBONY &amp; IVORY [A]</t>
+  </si>
+  <si>
+    <t>entelecheia [A]</t>
+  </si>
+  <si>
+    <t>fallen leaves -IIDX edition- [A]</t>
+  </si>
+  <si>
+    <t>FANTASTIC THREE [A]</t>
+  </si>
+  <si>
+    <t>Say YEEEAHH [A]</t>
+  </si>
+  <si>
+    <t>TOXIC VIBRATION [A]</t>
+  </si>
+  <si>
+    <t>表裏一体！？怪盗いいんちょの悩み♥ [A]</t>
+  </si>
+  <si>
+    <t>Cosmic Cat [L]</t>
+  </si>
+  <si>
+    <t>IMPLANTATION [L]</t>
+  </si>
+  <si>
+    <t>Dynamite [A]</t>
+  </si>
+  <si>
+    <t>M4K3 1T B0UNC3 [A]</t>
+  </si>
+  <si>
+    <t>POSSESSION [A]</t>
+  </si>
+  <si>
+    <t>refrain [A]</t>
+  </si>
+  <si>
+    <t>Triple Counter [A]</t>
+  </si>
+  <si>
+    <t>めいさいアイドル☆あいむちゃん♪ [A]</t>
+  </si>
+  <si>
+    <t>真 地獄超特急 -HELL or HELL- [A]</t>
+  </si>
+  <si>
+    <t>STARLIGHT DANCEHALL [L]</t>
+  </si>
+  <si>
+    <t>Super Duper Racers [L]</t>
+  </si>
+  <si>
+    <t>ZEPHYRANTHES [L]</t>
+  </si>
+  <si>
+    <t>Apocalypse [A]</t>
+  </si>
+  <si>
+    <t>Go Ahead!! [A]</t>
+  </si>
+  <si>
+    <t>OTENAMI Hurricane [A]</t>
+  </si>
+  <si>
+    <t>Sky High [A]</t>
+  </si>
+  <si>
+    <t>イザナミノナゲキ [A]</t>
+  </si>
+  <si>
+    <t>津軽雪 [A]</t>
+  </si>
+  <si>
+    <t>Boomy and The Boost [A]</t>
+  </si>
+  <si>
+    <t>DEATH†ZIGOQ ～怒りの高速爆走野郎～ [A]</t>
+  </si>
+  <si>
+    <t>DropZ-Line- [A]</t>
+  </si>
+  <si>
+    <t>Life Is A Game ft.DD"ナカタ"Metal [A]</t>
+  </si>
+  <si>
+    <t>Usual Days-remix [A]</t>
+  </si>
+  <si>
+    <t>シムルグの目醒め [A]</t>
+  </si>
+  <si>
+    <t>東京神話 [A]</t>
+  </si>
+  <si>
+    <t>ChaserXX [L]</t>
+  </si>
+  <si>
+    <t>O/D*20 [L]</t>
+  </si>
+  <si>
+    <t>dAuntl3ss [A]</t>
+  </si>
+  <si>
+    <t>Level One [A]</t>
+  </si>
+  <si>
+    <t>LOST TECHNOLOGIE [A]</t>
+  </si>
+  <si>
+    <t>Painful Fate [A]</t>
+  </si>
+  <si>
+    <t>Unbelief [A]</t>
+  </si>
+  <si>
+    <t>Xlø [A]</t>
+  </si>
+  <si>
+    <t>お菓子の王国 [A]</t>
+  </si>
+  <si>
+    <t>最小三倍完全数 [A]</t>
+  </si>
+  <si>
+    <t>Ember Lights [L]</t>
+  </si>
+  <si>
+    <t>龍王の霊廟(Mausoleum Of The Primal Dragon) [L]</t>
+  </si>
+  <si>
+    <t>Artist [A]</t>
+  </si>
+  <si>
+    <t>BEAT PRISONER [A]</t>
+  </si>
+  <si>
+    <t>Level 2 [A]</t>
+  </si>
+  <si>
+    <t>ORCA [A]</t>
+  </si>
+  <si>
+    <t>THE BRAVE MUST DIE [A]</t>
+  </si>
+  <si>
+    <t>がっつり陰キャ!? 怪盗いいんちょの億劫^^; [A]</t>
+  </si>
+  <si>
+    <t>Bow shock!! [L]</t>
+  </si>
+  <si>
+    <t>BLACK or WHITE? [A]</t>
+  </si>
+  <si>
+    <t>COSMIC RAY [A]</t>
+  </si>
+  <si>
+    <t>DUAL STRIKER [A]</t>
+  </si>
+  <si>
+    <t>Ignis†Iræ [A]</t>
+  </si>
+  <si>
+    <t>Level 3 [A]</t>
+  </si>
+  <si>
+    <t>LOCUS OF THE TRAVEL [A]</t>
+  </si>
+  <si>
+    <t>THE PEERLESS UNDER HEAVEN [A]</t>
+  </si>
+  <si>
+    <t>Viridian [A]</t>
+  </si>
+  <si>
+    <t>2 Beasts Unchained [A]</t>
+  </si>
+  <si>
+    <t>ABSOLUTE EVIL [A]</t>
+  </si>
+  <si>
+    <t>Flying Castle [A]</t>
+  </si>
+  <si>
+    <t>GRAVITON [A]</t>
+  </si>
+  <si>
+    <t>PLASMA SOUL NIGHT feat. Nana Takahashi / 709sec. [A]</t>
+  </si>
+  <si>
+    <t>Silver Bullet [A]</t>
+  </si>
+  <si>
+    <t>天邪鬼 [A]</t>
+  </si>
+  <si>
+    <t>逆月 [A]</t>
+  </si>
+  <si>
+    <t>ミュージック・アワー [L]</t>
+  </si>
+  <si>
+    <t>[ ]DENTITY [A]</t>
+  </si>
+  <si>
+    <t>Chaotoxin [A]</t>
+  </si>
+  <si>
+    <t>Level 4 [A]</t>
+  </si>
+  <si>
+    <t>LOUDER ROLLING THUNDER [A]</t>
+  </si>
+  <si>
+    <t>RINИE [A]</t>
+  </si>
+  <si>
+    <t>The Clown of 24stairs [A]</t>
+  </si>
+  <si>
+    <t>VØID [A]</t>
+  </si>
+  <si>
+    <t>VOLAQUAS [A]</t>
+  </si>
+  <si>
+    <t>儚キ戀ノ幻想譚 [A]</t>
+  </si>
+  <si>
+    <t>≡+≡ [L]</t>
+  </si>
+  <si>
+    <t>Caldwell 99 [L]</t>
+  </si>
+  <si>
+    <t>ちょえちょえまぎか [L]</t>
+  </si>
+  <si>
+    <t>Glitch N Ride [A]</t>
+  </si>
+  <si>
+    <t>Million Dollar [A]</t>
+  </si>
+  <si>
+    <t>SOLAR ECLIPSE [A]</t>
+  </si>
+  <si>
+    <t>The Last Apocalypse [A]</t>
+  </si>
+  <si>
+    <t>摩天楼 [A]</t>
+  </si>
+  <si>
+    <t>INHERITANCE [L]</t>
+  </si>
+  <si>
+    <t>destination [A]</t>
+  </si>
+  <si>
+    <t>Drop Syndicate [A]</t>
+  </si>
+  <si>
+    <t>Flämingo [A]</t>
+  </si>
+  <si>
+    <t>FlyAway [A]</t>
+  </si>
+  <si>
+    <t>hora de verdad [A]</t>
+  </si>
+  <si>
+    <t>Lightspeed [A]</t>
+  </si>
+  <si>
+    <t>MARLIN [A]</t>
+  </si>
+  <si>
+    <t>NOIXIA [A]</t>
+  </si>
+  <si>
+    <t>2 Be Continued [A]</t>
+  </si>
+  <si>
+    <t>Astra Blaze [A]</t>
+  </si>
+  <si>
+    <t>chaplet -IIDX re:build- [A]</t>
+  </si>
+  <si>
+    <t>HEROES [A]</t>
+  </si>
+  <si>
+    <t>RIZING-GAMERS. [A]</t>
+  </si>
+  <si>
+    <t>色を喪った街 [A]</t>
+  </si>
+  <si>
+    <t>DXY! [A]</t>
+  </si>
+  <si>
+    <t>minimalian [A]</t>
+  </si>
+  <si>
+    <t>Logic Board [A]</t>
+  </si>
+  <si>
+    <t>GENOCIDE [A]</t>
+  </si>
+  <si>
+    <t>Be quiet [L]</t>
+  </si>
+  <si>
+    <t>spiral galaxy [L]</t>
+  </si>
+  <si>
+    <t>冥 [A]</t>
+  </si>
+  <si>
+    <t>INAZUMA [L]</t>
+  </si>
+  <si>
+    <t>Little Little Princess [L]</t>
+  </si>
+  <si>
+    <t>DUE TOMORROW [A]</t>
+  </si>
+  <si>
+    <t>嘆きの樹 [A]</t>
+  </si>
+  <si>
+    <t>waxing and wanding [L]</t>
+  </si>
+  <si>
+    <t>Blue Rain [L]</t>
+  </si>
+  <si>
+    <t>Time to Air [L]</t>
+  </si>
+  <si>
+    <t>BITTER CHOCOLATE STRIKER [L]</t>
+  </si>
+  <si>
+    <t>ワルツ第17番 ト短調”大犬のワルツ” [A]</t>
+  </si>
+  <si>
+    <t>reunion [A]</t>
+  </si>
+  <si>
+    <t>DIAVOLO [A]</t>
+  </si>
+  <si>
+    <t>The Limbo [A]</t>
+  </si>
+  <si>
+    <t>君のハートにロックオン [A]</t>
+  </si>
+  <si>
+    <t>QUANTUM TELEPORTATION [L]</t>
+  </si>
+  <si>
+    <t>TITANS RETURN [L]</t>
+  </si>
+  <si>
+    <t>蛇神 [L]</t>
+  </si>
+  <si>
+    <t>STULTI [A]</t>
+  </si>
+  <si>
+    <t>Thor's Hammer [A]</t>
+  </si>
+  <si>
+    <t>ZED [L]</t>
+  </si>
+  <si>
+    <t>お米の美味しい炊き方、そしてお米を食べることによるその効果。 [L]</t>
+  </si>
+  <si>
+    <t>ra'am [A]</t>
+  </si>
+  <si>
+    <t>VOX UP [A]</t>
+  </si>
+  <si>
+    <t>煉獄のエルフェリア [A]</t>
+  </si>
+  <si>
+    <t>Ancient Scapes [L]</t>
+  </si>
+  <si>
+    <t>HYENA [L]</t>
+  </si>
+  <si>
+    <t>Flashes [A]</t>
+  </si>
+  <si>
+    <t>Reflux [A]</t>
+  </si>
+  <si>
+    <t>少年は空を辿る [A]</t>
+  </si>
+  <si>
+    <t>Flashes [L]</t>
+  </si>
+  <si>
+    <t>表裏一体！？怪盗いいんちょの悩み♥ [L]</t>
+  </si>
+  <si>
+    <t>DIAMOND CROSSING [A]</t>
+  </si>
+  <si>
+    <t>Grand Chariot [A]</t>
+  </si>
+  <si>
+    <t>NZM [A]</t>
+  </si>
+  <si>
+    <t>X [A]</t>
+  </si>
+  <si>
+    <t>灼熱 Pt.2 Long Train Running [A]</t>
+  </si>
+  <si>
+    <t>駅猫のワルツ [A]</t>
+  </si>
+  <si>
+    <t>Violet Pulse [L]</t>
+  </si>
+  <si>
+    <t>Welcome [L]</t>
+  </si>
+  <si>
+    <t>紫陽花 -AZISAI- [L]</t>
+  </si>
+  <si>
+    <t>ECHIDNA [A]</t>
+  </si>
+  <si>
+    <t>GuNGNiR [A]</t>
+  </si>
+  <si>
+    <t>焔極OVERKILL [A]</t>
+  </si>
+  <si>
+    <t>SAMURAI-Scramble [L]</t>
+  </si>
+  <si>
+    <t>REVOLVER [L]</t>
+  </si>
+  <si>
+    <t>Dr. Chemical &amp; Killing Machine [A]</t>
+  </si>
+  <si>
+    <t>Necroxis Girl [A]</t>
+  </si>
+  <si>
+    <t>The Rebellion of Sequencer [A]</t>
+  </si>
+  <si>
+    <t>CODE:Ø [L]</t>
+  </si>
+  <si>
+    <t>Everlasting Message [A]</t>
+  </si>
+  <si>
+    <t>Inferno of Fomalhaut [A]</t>
+  </si>
+  <si>
+    <t>Smashing Wedge [A]</t>
+  </si>
+  <si>
+    <t>THE F∀UST [A]</t>
+  </si>
+  <si>
+    <t>魅惑のYUMMYスイーツ [A]</t>
+  </si>
+  <si>
+    <t>-65℃ [A]</t>
+  </si>
+  <si>
+    <t>∀ [A]</t>
+  </si>
+  <si>
+    <t>MEGAERA [A]</t>
+  </si>
+  <si>
+    <t>二人ノ廃城幽踊宴 [A]</t>
+  </si>
+  <si>
+    <t>伐折羅-vajra- [A]</t>
+  </si>
+  <si>
+    <t>閠槞彁の願い [A]</t>
+  </si>
+  <si>
+    <t>Arkadia [A]</t>
+  </si>
+  <si>
+    <t>hard-wired [A]</t>
+  </si>
+  <si>
+    <t>RAGE feat.H14 of LEONAIR [A]</t>
+  </si>
+  <si>
+    <t>WHA [A]</t>
+  </si>
+  <si>
+    <t>Bad Encryption [A]</t>
+  </si>
+  <si>
+    <t>suspicions [A]</t>
+  </si>
+  <si>
+    <t>栄冠のカンパネラ [A]</t>
+  </si>
+  <si>
+    <t>Ambivalent Vermilia [A]</t>
+  </si>
+  <si>
+    <t>CADENZA [A]</t>
+  </si>
+  <si>
+    <t>Demon March [A]</t>
+  </si>
+  <si>
+    <t>Level 5 [A]</t>
+  </si>
+  <si>
+    <t>Vulnerability [A]</t>
+  </si>
+  <si>
+    <t>Submerge Serenade [L]</t>
+  </si>
+  <si>
+    <t>Cross Fire [A]</t>
+  </si>
+  <si>
+    <t>God Mind [A]</t>
+  </si>
+  <si>
+    <t>uən [A]</t>
+  </si>
+  <si>
+    <t>Without Heaven [A]</t>
+  </si>
+  <si>
+    <t>アラビアン ハイパー ナイト [A]</t>
+  </si>
+  <si>
+    <t>スキッテイエェエエェ!!!! [A]</t>
+  </si>
+  <si>
+    <t>天使のカンタータ -Cantata of Angels- [A]</t>
+  </si>
+  <si>
+    <t>⁽⁽ଘ( ˙꒳˙ )ଓ⁾⁾ beyond reason [A]</t>
+  </si>
+  <si>
+    <t>Amor∞Fati [A]</t>
+  </si>
+  <si>
+    <t>fixer [A]</t>
+  </si>
+  <si>
+    <t>FiZZλ_PØT!0И [A]</t>
+  </si>
+  <si>
+    <t>PERFECT GREAT!! [A]</t>
+  </si>
+  <si>
+    <t>RUINA [A]</t>
+  </si>
+  <si>
+    <t>quasar [A]</t>
+  </si>
+  <si>
+    <t>ピアノ協奏曲第１番”蠍火” [A]</t>
+  </si>
+  <si>
+    <t>CONTRACT [L]</t>
+  </si>
+  <si>
+    <t>TRANOID [L]</t>
+  </si>
+  <si>
+    <t>VANESSA [L]</t>
+  </si>
+  <si>
+    <t>MENDES [A]</t>
+  </si>
+  <si>
+    <t>PARANOiA ～HADES～ [A]</t>
+  </si>
+  <si>
+    <t>Anisakis -somatic mutation type"Forza"- [L]</t>
+  </si>
+  <si>
+    <t>Do it!! Do it!! [L]</t>
+  </si>
+  <si>
+    <t>four pieces of heaven [L]</t>
+  </si>
+  <si>
+    <t>卑弥呼 [A]</t>
+  </si>
+  <si>
+    <t>Bad Maniacs [A]</t>
+  </si>
+  <si>
+    <t>SOLID STATE SQUAD [L]</t>
+  </si>
+  <si>
+    <t>PARADISE LOST [A]</t>
+  </si>
+  <si>
+    <t>天空の夜明け [A]</t>
+  </si>
+  <si>
+    <t>Confiserie [A]</t>
+  </si>
+  <si>
+    <t>Elemental Creation [A]</t>
+  </si>
+  <si>
+    <t>Saturn [L]</t>
+  </si>
+  <si>
+    <t>IX [A]</t>
+  </si>
+  <si>
+    <t>Sigmund [A]</t>
+  </si>
+  <si>
+    <t>Elektrick U-Phoria [L]</t>
+  </si>
+  <si>
+    <t>Verflucht [L]</t>
+  </si>
+  <si>
+    <t>疾風迅雷 [L]</t>
+  </si>
+  <si>
+    <t>共鳴遊戯の華 [A]</t>
+  </si>
+  <si>
+    <t>#The_Relentless [L]</t>
+  </si>
+  <si>
+    <t>EBONY &amp; IVORY [L]</t>
+  </si>
+  <si>
+    <t>千年ノ理 [L]</t>
+  </si>
+  <si>
+    <t>GOBBLE [H]</t>
+  </si>
+  <si>
+    <t>CODE:1 [revision1.0.1] [A]</t>
+  </si>
+  <si>
+    <t>SEQUENCE CAT [A]</t>
+  </si>
+  <si>
+    <t>EMERALDAS [A]</t>
+  </si>
+  <si>
+    <t>HYPE THE CORE [A]</t>
+  </si>
+  <si>
+    <t>Initiation [A]</t>
+  </si>
+  <si>
+    <t>Carmina [A]</t>
+  </si>
+  <si>
+    <t>X-DEN [A]</t>
+  </si>
+  <si>
+    <t>CoMAAAAAAA [L]</t>
+  </si>
+  <si>
+    <t>ピアノ協奏曲第1番”蠍火” (BlackY Remix) [A]</t>
+  </si>
+  <si>
+    <t>LIGHTNING STRIKES [L]</t>
+  </si>
+  <si>
+    <t>Lost Souls [L]</t>
+  </si>
+  <si>
+    <t>Override [L]</t>
+  </si>
+  <si>
+    <t>Sinus Iridum [A]</t>
+  </si>
+  <si>
+    <t>ディスコルディア [A]</t>
+  </si>
+  <si>
+    <t>Binary Black Hole [A]</t>
+  </si>
+  <si>
+    <t>SOLID WYVERN [L]</t>
+  </si>
+  <si>
+    <t>Beyond Evolution [A]</t>
+  </si>
+  <si>
+    <t>Xerulean [A]</t>
+  </si>
+  <si>
+    <t>惑星鉄道 [A]</t>
+  </si>
+  <si>
+    <t>Skratch Education Lv-1 [A]</t>
+  </si>
+  <si>
+    <t>Uaigh Gealaí [A]</t>
+  </si>
+  <si>
+    <t>XHRONOXAPSULΞ [A]</t>
+  </si>
+  <si>
+    <t>Memoria Obscura [A]</t>
+  </si>
+  <si>
+    <t>ιgniЯRuina [A]</t>
+  </si>
+  <si>
+    <t>Lisa-RICCIA [L]</t>
+  </si>
+  <si>
+    <t>NEMESIS [A]</t>
+  </si>
+  <si>
+    <t>KAMAITACHI [L]</t>
+  </si>
+  <si>
+    <t>ICARUS [L]</t>
+  </si>
+  <si>
+    <t>STEEL NEEDLE [L]</t>
+  </si>
+  <si>
+    <t>Almagest [A]</t>
+  </si>
+  <si>
+    <t>quell～the seventh slave～ [A]</t>
+  </si>
+  <si>
+    <t>perditus†paradisus [A]</t>
+  </si>
+  <si>
+    <t>Dances with Snow Fairies [L]</t>
+  </si>
+  <si>
+    <t>QUANTUM TELEPORTATION [A]</t>
+  </si>
+  <si>
+    <t>Phoenix [L]</t>
+  </si>
+  <si>
+    <t>The Limbo [L]</t>
+  </si>
+  <si>
+    <t>聖人の塔 [L]</t>
+  </si>
+  <si>
+    <t>†渚の小悪魔ラヴリィ～レイディオ†(IIDX EDIT) [A]</t>
+  </si>
+  <si>
+    <t>Illegal Function Call [L]</t>
+  </si>
+  <si>
+    <t>KAISER PHOENIX [L]</t>
+  </si>
+  <si>
+    <t>Sigmund [L]</t>
+  </si>
+  <si>
+    <t>Chrono Diver -PENDULUMs- [A]</t>
+  </si>
+  <si>
+    <t>CHRONO DIVER -NORNIR- [L]</t>
+  </si>
+  <si>
+    <t>超青少年ノ為ノ超多幸ナ超古典的超舞曲 [L]</t>
+  </si>
+  <si>
+    <t>Mare Nectaris [A]</t>
+  </si>
+  <si>
+    <t>BroGamer [L]</t>
+  </si>
+  <si>
+    <t>GuNGNiR [L]</t>
+  </si>
+  <si>
+    <t>DEATH†ZIGOQ ～怒りの高速爆走野郎～ [L]</t>
+  </si>
+  <si>
+    <t>EROICA [A]</t>
+  </si>
+  <si>
+    <t>n/a [A]</t>
+  </si>
+  <si>
+    <t>ピアノ独奏無言歌 "灰燼" [A]</t>
+  </si>
+  <si>
+    <t>Somnidiscotheque [A]</t>
+  </si>
+  <si>
+    <t>SμG@R RU$# [A]</t>
+  </si>
+  <si>
+    <t>12.0</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>LV.x</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -5187,7 +7383,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5265,6 +7461,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -88196,4 +90395,5855 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{916CA30D-4175-5B49-A1DB-08C6426A8024}">
+  <dimension ref="A2:B731"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetData>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>11.6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>11.6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>11.8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>11.8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>11.8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>11.8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>11.8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>11.8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11.8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11.8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>11.8</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>11.8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>11.8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>11.8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>11.8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>11.8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>11.8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>11.8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>11.8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>11.8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>11.8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>11.8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>11.8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>11.8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>11.8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>11.8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>11.8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1505</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="26" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>12.1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>12.1</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>12.1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>12.1</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>12.1</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>12.1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>12.1</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>12.1</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>12.1</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>12.1</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>12.1</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>12.1</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>12.1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>12.1</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>12.1</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>12.1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>12.1</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>12.1</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>12.1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>12.1</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>12.1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>12.1</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>12.1</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>12.1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>12.1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>12.1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>12.1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>12.1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>12.1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>12.1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>12.1</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>12.1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>12.1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>12.1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>12.1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>12.1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>12.1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>12.1</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>12.1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>12.1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>12.1</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>12.1</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>12.1</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>12.1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>12.1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>12.1</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>12.1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>12.1</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>12.1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>12.1</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>12.1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>12.1</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>12.1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>12.1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>12.1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>12.1</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>12.1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>12.1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>12.1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>12.1</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>12.1</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>12.1</v>
+      </c>
+      <c r="B151" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>12.1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>12.1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>12.1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>12.1</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>12.1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>12.1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>12.1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>12.1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>12.1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>12.1</v>
+      </c>
+      <c r="B161" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>12.1</v>
+      </c>
+      <c r="B162" t="s">
+        <v>1582</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>12.1</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>12.2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>12.2</v>
+      </c>
+      <c r="B165" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>12.2</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>12.2</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>12.2</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>12.2</v>
+      </c>
+      <c r="B169" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>12.2</v>
+      </c>
+      <c r="B170" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>12.2</v>
+      </c>
+      <c r="B171" t="s">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>12.2</v>
+      </c>
+      <c r="B172" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>12.2</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>12.2</v>
+      </c>
+      <c r="B174" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>12.2</v>
+      </c>
+      <c r="B175" t="s">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>12.2</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>12.2</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>12.2</v>
+      </c>
+      <c r="B178" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>12.2</v>
+      </c>
+      <c r="B179" t="s">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>12.2</v>
+      </c>
+      <c r="B180" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>12.2</v>
+      </c>
+      <c r="B181" t="s">
+        <v>1601</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>12.2</v>
+      </c>
+      <c r="B182" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>12.2</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>12.2</v>
+      </c>
+      <c r="B184" t="s">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>12.2</v>
+      </c>
+      <c r="B185" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>12.2</v>
+      </c>
+      <c r="B186" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>12.2</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>12.2</v>
+      </c>
+      <c r="B188" t="s">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>12.2</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>12.2</v>
+      </c>
+      <c r="B190" t="s">
+        <v>1610</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>12.2</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>12.2</v>
+      </c>
+      <c r="B192" t="s">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>12.2</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>12.2</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>12.2</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>12.2</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>12.2</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>12.2</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>12.2</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>12.2</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>12.2</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>12.2</v>
+      </c>
+      <c r="B202" t="s">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>12.2</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>12.2</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>12.2</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>12.2</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>12.2</v>
+      </c>
+      <c r="B207" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>12.2</v>
+      </c>
+      <c r="B208" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>12.2</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>12.2</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>12.2</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>12.2</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>12.2</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>12.2</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>12.2</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>12.2</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>12.2</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>12.2</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>12.2</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>12.2</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>12.2</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1641</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>12.2</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>12.2</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>12.2</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>12.2</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>12.2</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>12.2</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>12.2</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>12.2</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>12.2</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>12.2</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>12.2</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>12.2</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>12.2</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>12.2</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>12.2</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>12.2</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>12.2</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>12.2</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>12.2</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>12.2</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>12.2</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>12.2</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>12.2</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>12.2</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>12.2</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>12.2</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>12.2</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>12.2</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>12.2</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>12.2</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>12.2</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>12.3</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>12.3</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>12.3</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>12.3</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>12.3</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>12.3</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>12.3</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>12.3</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>12.3</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>12.3</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>12.3</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>12.3</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>12.3</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>12.3</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>12.3</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>12.3</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>12.3</v>
+      </c>
+      <c r="B269" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>12.3</v>
+      </c>
+      <c r="B270" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>12.3</v>
+      </c>
+      <c r="B271" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>12.3</v>
+      </c>
+      <c r="B272" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>12.3</v>
+      </c>
+      <c r="B273" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>12.3</v>
+      </c>
+      <c r="B274" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>12.3</v>
+      </c>
+      <c r="B275" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>12.3</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>12.3</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>12.3</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>12.3</v>
+      </c>
+      <c r="B279" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>12.3</v>
+      </c>
+      <c r="B280" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>12.3</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>12.3</v>
+      </c>
+      <c r="B282" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>12.3</v>
+      </c>
+      <c r="B283" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>12.3</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>12.3</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>12.3</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>12.3</v>
+      </c>
+      <c r="B287" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>12.3</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>12.3</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>12.3</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>12.3</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>12.3</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>12.3</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>12.3</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>12.3</v>
+      </c>
+      <c r="B295" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>12.3</v>
+      </c>
+      <c r="B296" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>12.3</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>12.3</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>12.3</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>12.3</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>12.3</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>12.3</v>
+      </c>
+      <c r="B302" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>12.3</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>12.3</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>12.3</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>12.3</v>
+      </c>
+      <c r="B306" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>12.3</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>12.3</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>12.3</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>12.3</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>12.3</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>12.3</v>
+      </c>
+      <c r="B312" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>12.3</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>12.3</v>
+      </c>
+      <c r="B314" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>12.3</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>12.3</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>12.3</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>12.3</v>
+      </c>
+      <c r="B318" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>12.3</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>12.3</v>
+      </c>
+      <c r="B320" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>12.3</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>12.3</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>12.3</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>12.3</v>
+      </c>
+      <c r="B324" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>12.3</v>
+      </c>
+      <c r="B325" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>12.3</v>
+      </c>
+      <c r="B326" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>12.3</v>
+      </c>
+      <c r="B327" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>12.3</v>
+      </c>
+      <c r="B328" t="s">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>12.3</v>
+      </c>
+      <c r="B329" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>12.3</v>
+      </c>
+      <c r="B330" t="s">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>12.3</v>
+      </c>
+      <c r="B331" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>12.3</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>12.3</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>12.3</v>
+      </c>
+      <c r="B334" t="s">
+        <v>1754</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>12.3</v>
+      </c>
+      <c r="B335" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>12.3</v>
+      </c>
+      <c r="B336" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>12.3</v>
+      </c>
+      <c r="B337" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>12.3</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>12.3</v>
+      </c>
+      <c r="B339" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>12.3</v>
+      </c>
+      <c r="B340" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>12.3</v>
+      </c>
+      <c r="B341" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>12.3</v>
+      </c>
+      <c r="B342" t="s">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>12.3</v>
+      </c>
+      <c r="B343" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>12.3</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1764</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>12.3</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>12.3</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>12.3</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>12.3</v>
+      </c>
+      <c r="B348" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>12.3</v>
+      </c>
+      <c r="B349" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>12.3</v>
+      </c>
+      <c r="B350" t="s">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>12.3</v>
+      </c>
+      <c r="B351" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>12.3</v>
+      </c>
+      <c r="B352" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>12.3</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>12.3</v>
+      </c>
+      <c r="B354" t="s">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>12.3</v>
+      </c>
+      <c r="B355" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>12.3</v>
+      </c>
+      <c r="B356" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>12.3</v>
+      </c>
+      <c r="B357" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>12.3</v>
+      </c>
+      <c r="B358" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>12.3</v>
+      </c>
+      <c r="B359" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>12.3</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>12.3</v>
+      </c>
+      <c r="B361" t="s">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>12.3</v>
+      </c>
+      <c r="B362" t="s">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>12.3</v>
+      </c>
+      <c r="B363" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>12.3</v>
+      </c>
+      <c r="B364" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>12.3</v>
+      </c>
+      <c r="B365" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>12.3</v>
+      </c>
+      <c r="B366" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>12.3</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>12.3</v>
+      </c>
+      <c r="B368" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>12.3</v>
+      </c>
+      <c r="B369" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>12.3</v>
+      </c>
+      <c r="B370" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>12.3</v>
+      </c>
+      <c r="B371" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>12.3</v>
+      </c>
+      <c r="B372" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>12.3</v>
+      </c>
+      <c r="B373" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>12.3</v>
+      </c>
+      <c r="B374" t="s">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>12.3</v>
+      </c>
+      <c r="B375" t="s">
+        <v>1795</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>12.3</v>
+      </c>
+      <c r="B376" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>12.3</v>
+      </c>
+      <c r="B377" t="s">
+        <v>1797</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>12.3</v>
+      </c>
+      <c r="B378" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>12.3</v>
+      </c>
+      <c r="B379" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>12.3</v>
+      </c>
+      <c r="B380" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>12.3</v>
+      </c>
+      <c r="B381" t="s">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>12.3</v>
+      </c>
+      <c r="B382" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>12.3</v>
+      </c>
+      <c r="B383" t="s">
+        <v>1803</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>12.3</v>
+      </c>
+      <c r="B384" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>12.3</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>12.3</v>
+      </c>
+      <c r="B386" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>12.3</v>
+      </c>
+      <c r="B387" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>12.3</v>
+      </c>
+      <c r="B388" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>12.3</v>
+      </c>
+      <c r="B389" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>12.3</v>
+      </c>
+      <c r="B390" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>12.3</v>
+      </c>
+      <c r="B391" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>12.3</v>
+      </c>
+      <c r="B392" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>12.3</v>
+      </c>
+      <c r="B393" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>12.3</v>
+      </c>
+      <c r="B394" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>12.3</v>
+      </c>
+      <c r="B395" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>12.3</v>
+      </c>
+      <c r="B396" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>12.3</v>
+      </c>
+      <c r="B397" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>12.3</v>
+      </c>
+      <c r="B398" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>12.3</v>
+      </c>
+      <c r="B399" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>12.3</v>
+      </c>
+      <c r="B400" t="s">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>12.3</v>
+      </c>
+      <c r="B401" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>12.3</v>
+      </c>
+      <c r="B402" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>12.3</v>
+      </c>
+      <c r="B403" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>12.3</v>
+      </c>
+      <c r="B404" t="s">
+        <v>1824</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>12.3</v>
+      </c>
+      <c r="B405" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>12.3</v>
+      </c>
+      <c r="B406" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>12.3</v>
+      </c>
+      <c r="B407" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>12.3</v>
+      </c>
+      <c r="B408" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>12.4</v>
+      </c>
+      <c r="B409" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>12.4</v>
+      </c>
+      <c r="B410" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>12.4</v>
+      </c>
+      <c r="B411" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>12.4</v>
+      </c>
+      <c r="B412" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>12.4</v>
+      </c>
+      <c r="B413" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>12.4</v>
+      </c>
+      <c r="B414" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>12.4</v>
+      </c>
+      <c r="B415" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>12.4</v>
+      </c>
+      <c r="B416" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>12.4</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>12.4</v>
+      </c>
+      <c r="B418" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>12.4</v>
+      </c>
+      <c r="B419" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>12.4</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>12.4</v>
+      </c>
+      <c r="B421" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>12.4</v>
+      </c>
+      <c r="B422" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>12.4</v>
+      </c>
+      <c r="B423" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>12.4</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>12.4</v>
+      </c>
+      <c r="B425" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>12.4</v>
+      </c>
+      <c r="B426" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>12.4</v>
+      </c>
+      <c r="B427" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>12.4</v>
+      </c>
+      <c r="B428" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>12.4</v>
+      </c>
+      <c r="B429" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>12.4</v>
+      </c>
+      <c r="B430" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>12.4</v>
+      </c>
+      <c r="B431" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>12.4</v>
+      </c>
+      <c r="B432" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>12.4</v>
+      </c>
+      <c r="B433" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>12.4</v>
+      </c>
+      <c r="B434" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>12.4</v>
+      </c>
+      <c r="B435" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>12.4</v>
+      </c>
+      <c r="B436" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>12.4</v>
+      </c>
+      <c r="B437" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>12.4</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>12.4</v>
+      </c>
+      <c r="B439" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>12.4</v>
+      </c>
+      <c r="B440" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>12.4</v>
+      </c>
+      <c r="B441" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>12.4</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>12.4</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>12.4</v>
+      </c>
+      <c r="B444" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>12.4</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>12.4</v>
+      </c>
+      <c r="B446" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>12.4</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>12.4</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>12.4</v>
+      </c>
+      <c r="B449" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>12.4</v>
+      </c>
+      <c r="B450" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>12.4</v>
+      </c>
+      <c r="B451" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>12.4</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>12.4</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>12.4</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>12.4</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>12.4</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>12.4</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>12.4</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>12.4</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>12.4</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>12.4</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>12.4</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>12.4</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>12.4</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>12.4</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>12.4</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>12.4</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>12.4</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>12.4</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>12.4</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>12.4</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>12.4</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>12.4</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>12.4</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>12.4</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>12.4</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>12.4</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>12.4</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>12.4</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>12.4</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>12.4</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>12.4</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>12.4</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>12.4</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>12.4</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>12.4</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>12.4</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>12.4</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>12.4</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>12.4</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>12.4</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>12.4</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>12.4</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>12.4</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>12.4</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>12.4</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>12.4</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>12.4</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>12.4</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>12.4</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>12.4</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>12.4</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>12.4</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>12.4</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>12.4</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>12.4</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>12.4</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>12.4</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>12.4</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>12.4</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>12.4</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>12.4</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>12.4</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>12.4</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>12.4</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>12.4</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>12.4</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>12.4</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>12.4</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>12.4</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>12.4</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>12.4</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>12.4</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>12.4</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>12.4</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>12.4</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>12.4</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>12.4</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>12.4</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>12.4</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>12.4</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>12.4</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>12.4</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>12.4</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>12.4</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>12.4</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>12.4</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>12.4</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>12.4</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>12.4</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>12.4</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>12.4</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>12.4</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>12.4</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>12.4</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>12.4</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>12.4</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>12.4</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>12.4</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>12.4</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>12.4</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>12.4</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>12.4</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>12.4</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>12.4</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>12.4</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>12.4</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>12.4</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>12.5</v>
+      </c>
+      <c r="B559" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>12.5</v>
+      </c>
+      <c r="B560" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>12.5</v>
+      </c>
+      <c r="B561" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>12.5</v>
+      </c>
+      <c r="B562" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>12.5</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>12.5</v>
+      </c>
+      <c r="B564" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>12.5</v>
+      </c>
+      <c r="B565" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>12.5</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>12.5</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>12.5</v>
+      </c>
+      <c r="B568" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>12.5</v>
+      </c>
+      <c r="B569" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>12.5</v>
+      </c>
+      <c r="B570" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>12.5</v>
+      </c>
+      <c r="B571" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>12.5</v>
+      </c>
+      <c r="B572" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>12.5</v>
+      </c>
+      <c r="B573" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>12.5</v>
+      </c>
+      <c r="B574" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>12.5</v>
+      </c>
+      <c r="B575" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>12.5</v>
+      </c>
+      <c r="B576" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>12.5</v>
+      </c>
+      <c r="B577" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>12.5</v>
+      </c>
+      <c r="B578" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>12.5</v>
+      </c>
+      <c r="B579" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>12.5</v>
+      </c>
+      <c r="B580" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>12.5</v>
+      </c>
+      <c r="B581" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>12.5</v>
+      </c>
+      <c r="B582" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>12.5</v>
+      </c>
+      <c r="B583" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>12.5</v>
+      </c>
+      <c r="B584" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>12.5</v>
+      </c>
+      <c r="B585" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>12.5</v>
+      </c>
+      <c r="B586" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>12.5</v>
+      </c>
+      <c r="B587" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>12.5</v>
+      </c>
+      <c r="B588" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>12.5</v>
+      </c>
+      <c r="B589" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>12.5</v>
+      </c>
+      <c r="B590" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>12.5</v>
+      </c>
+      <c r="B591" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>12.5</v>
+      </c>
+      <c r="B592" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>12.5</v>
+      </c>
+      <c r="B593" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>12.5</v>
+      </c>
+      <c r="B594" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>12.5</v>
+      </c>
+      <c r="B595" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>12.5</v>
+      </c>
+      <c r="B596" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>12.5</v>
+      </c>
+      <c r="B597" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>12.5</v>
+      </c>
+      <c r="B598" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>12.5</v>
+      </c>
+      <c r="B599" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>12.5</v>
+      </c>
+      <c r="B600" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>12.5</v>
+      </c>
+      <c r="B601" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>12.5</v>
+      </c>
+      <c r="B602" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>12.5</v>
+      </c>
+      <c r="B603" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>12.5</v>
+      </c>
+      <c r="B604" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>12.5</v>
+      </c>
+      <c r="B605" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>12.5</v>
+      </c>
+      <c r="B606" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>12.5</v>
+      </c>
+      <c r="B607" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>12.5</v>
+      </c>
+      <c r="B608" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>12.5</v>
+      </c>
+      <c r="B609" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>12.5</v>
+      </c>
+      <c r="B610" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>12.5</v>
+      </c>
+      <c r="B611" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>12.5</v>
+      </c>
+      <c r="B612" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>12.5</v>
+      </c>
+      <c r="B613" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>12.5</v>
+      </c>
+      <c r="B614" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>12.5</v>
+      </c>
+      <c r="B615" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>12.5</v>
+      </c>
+      <c r="B616" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>12.5</v>
+      </c>
+      <c r="B617" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>12.5</v>
+      </c>
+      <c r="B618" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>12.5</v>
+      </c>
+      <c r="B619" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>12.5</v>
+      </c>
+      <c r="B620" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>12.5</v>
+      </c>
+      <c r="B621" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>12.5</v>
+      </c>
+      <c r="B622" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>12.5</v>
+      </c>
+      <c r="B623" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>12.5</v>
+      </c>
+      <c r="B624" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>12.5</v>
+      </c>
+      <c r="B625" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>12.5</v>
+      </c>
+      <c r="B626" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>12.5</v>
+      </c>
+      <c r="B627" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>12.5</v>
+      </c>
+      <c r="B628" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>12.5</v>
+      </c>
+      <c r="B629" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>12.5</v>
+      </c>
+      <c r="B630" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>12.5</v>
+      </c>
+      <c r="B631" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>12.5</v>
+      </c>
+      <c r="B632" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>12.5</v>
+      </c>
+      <c r="B633" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>12.5</v>
+      </c>
+      <c r="B634" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>12.5</v>
+      </c>
+      <c r="B635" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>12.5</v>
+      </c>
+      <c r="B636" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>12.5</v>
+      </c>
+      <c r="B637" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>12.5</v>
+      </c>
+      <c r="B638" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>12.5</v>
+      </c>
+      <c r="B639" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>12.5</v>
+      </c>
+      <c r="B640" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>12.5</v>
+      </c>
+      <c r="B641" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>12.5</v>
+      </c>
+      <c r="B642" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>12.5</v>
+      </c>
+      <c r="B643" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>12.5</v>
+      </c>
+      <c r="B644" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>12.5</v>
+      </c>
+      <c r="B645" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>12.5</v>
+      </c>
+      <c r="B646" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>12.5</v>
+      </c>
+      <c r="B647" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>12.5</v>
+      </c>
+      <c r="B648" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>12.5</v>
+      </c>
+      <c r="B649" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>12.5</v>
+      </c>
+      <c r="B650" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>12.6</v>
+      </c>
+      <c r="B651" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>12.6</v>
+      </c>
+      <c r="B652" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>12.6</v>
+      </c>
+      <c r="B653" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>12.6</v>
+      </c>
+      <c r="B654" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>12.6</v>
+      </c>
+      <c r="B655" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>12.6</v>
+      </c>
+      <c r="B656" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>12.6</v>
+      </c>
+      <c r="B657" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>12.6</v>
+      </c>
+      <c r="B658" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>12.6</v>
+      </c>
+      <c r="B659" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>12.6</v>
+      </c>
+      <c r="B660" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>12.6</v>
+      </c>
+      <c r="B661" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>12.6</v>
+      </c>
+      <c r="B662" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>12.6</v>
+      </c>
+      <c r="B663" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>12.6</v>
+      </c>
+      <c r="B664" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>12.6</v>
+      </c>
+      <c r="B665" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>12.6</v>
+      </c>
+      <c r="B666" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>12.6</v>
+      </c>
+      <c r="B667" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>12.6</v>
+      </c>
+      <c r="B668" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>12.6</v>
+      </c>
+      <c r="B669" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>12.6</v>
+      </c>
+      <c r="B670" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>12.6</v>
+      </c>
+      <c r="B671" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>12.6</v>
+      </c>
+      <c r="B672" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>12.6</v>
+      </c>
+      <c r="B673" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>12.6</v>
+      </c>
+      <c r="B674" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>12.6</v>
+      </c>
+      <c r="B675" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>12.6</v>
+      </c>
+      <c r="B676" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>12.6</v>
+      </c>
+      <c r="B677" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>12.6</v>
+      </c>
+      <c r="B678" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>12.6</v>
+      </c>
+      <c r="B679" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>12.6</v>
+      </c>
+      <c r="B680" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>12.6</v>
+      </c>
+      <c r="B681" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>12.6</v>
+      </c>
+      <c r="B682" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>12.6</v>
+      </c>
+      <c r="B683" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>12.6</v>
+      </c>
+      <c r="B684" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>12.6</v>
+      </c>
+      <c r="B685" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>12.6</v>
+      </c>
+      <c r="B686" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>12.6</v>
+      </c>
+      <c r="B687" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>12.6</v>
+      </c>
+      <c r="B688" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>12.6</v>
+      </c>
+      <c r="B689" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>12.6</v>
+      </c>
+      <c r="B690" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>12.6</v>
+      </c>
+      <c r="B691" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>12.6</v>
+      </c>
+      <c r="B692" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>12.6</v>
+      </c>
+      <c r="B693" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>12.6</v>
+      </c>
+      <c r="B694" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>12.6</v>
+      </c>
+      <c r="B695" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>12.6</v>
+      </c>
+      <c r="B696" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>12.6</v>
+      </c>
+      <c r="B697" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>12.6</v>
+      </c>
+      <c r="B698" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>12.6</v>
+      </c>
+      <c r="B699" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>12.6</v>
+      </c>
+      <c r="B700" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>12.6</v>
+      </c>
+      <c r="B701" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>12.6</v>
+      </c>
+      <c r="B702" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>12.6</v>
+      </c>
+      <c r="B703" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>12.7</v>
+      </c>
+      <c r="B704" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>12.7</v>
+      </c>
+      <c r="B705" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>12.7</v>
+      </c>
+      <c r="B706" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>12.7</v>
+      </c>
+      <c r="B707" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>12.7</v>
+      </c>
+      <c r="B708" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>12.7</v>
+      </c>
+      <c r="B709" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>12.7</v>
+      </c>
+      <c r="B710" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>12.7</v>
+      </c>
+      <c r="B711" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>12.7</v>
+      </c>
+      <c r="B712" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>12.7</v>
+      </c>
+      <c r="B713" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>12.7</v>
+      </c>
+      <c r="B714" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>12.7</v>
+      </c>
+      <c r="B715" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>12.7</v>
+      </c>
+      <c r="B716" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>12.7</v>
+      </c>
+      <c r="B717" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>12.7</v>
+      </c>
+      <c r="B718" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>12.7</v>
+      </c>
+      <c r="B719" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>12.7</v>
+      </c>
+      <c r="B720" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>12.7</v>
+      </c>
+      <c r="B721" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>12.7</v>
+      </c>
+      <c r="B722" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>12.7</v>
+      </c>
+      <c r="B723" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>12.7</v>
+      </c>
+      <c r="B724" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>12.7</v>
+      </c>
+      <c r="B725" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>12.7</v>
+      </c>
+      <c r="B726" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>12.7</v>
+      </c>
+      <c r="B727" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>12.7</v>
+      </c>
+      <c r="B728" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>12.7</v>
+      </c>
+      <c r="B729" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>12.7</v>
+      </c>
+      <c r="B730" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>12.7</v>
+      </c>
+      <c r="B731" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>